--- a/output/version3/test/15-10/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>646</v>
+        <v>776</v>
       </c>
       <c r="C2" t="n">
-        <v>555</v>
+        <v>609</v>
       </c>
       <c r="D2" t="n">
-        <v>719</v>
+        <v>596</v>
       </c>
       <c r="E2" t="n">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="F2" t="n">
-        <v>722</v>
+        <v>648</v>
       </c>
       <c r="G2" t="n">
-        <v>638</v>
+        <v>562</v>
       </c>
       <c r="H2" t="n">
-        <v>610</v>
+        <v>586</v>
       </c>
       <c r="I2" t="n">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>627</v>
+        <v>687</v>
       </c>
       <c r="L2" t="n">
-        <v>631.4</v>
+        <v>633.6</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>579</v>
+        <v>493</v>
       </c>
       <c r="C3" t="n">
-        <v>574</v>
+        <v>742</v>
       </c>
       <c r="D3" t="n">
-        <v>664</v>
+        <v>677</v>
       </c>
       <c r="E3" t="n">
-        <v>727</v>
+        <v>628</v>
       </c>
       <c r="F3" t="n">
-        <v>781</v>
+        <v>672</v>
       </c>
       <c r="G3" t="n">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="H3" t="n">
-        <v>608</v>
+        <v>788</v>
       </c>
       <c r="I3" t="n">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="K3" t="n">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="L3" t="n">
-        <v>636.7</v>
+        <v>642.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>745</v>
+        <v>557</v>
       </c>
       <c r="C4" t="n">
-        <v>596</v>
+        <v>647</v>
       </c>
       <c r="D4" t="n">
-        <v>669</v>
+        <v>575</v>
       </c>
       <c r="E4" t="n">
-        <v>540</v>
+        <v>668</v>
       </c>
       <c r="F4" t="n">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="G4" t="n">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H4" t="n">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="I4" t="n">
-        <v>664</v>
+        <v>586</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="K4" t="n">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="L4" t="n">
-        <v>614.6</v>
+        <v>599.5</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>706</v>
+        <v>631</v>
       </c>
       <c r="C5" t="n">
-        <v>630</v>
+        <v>697</v>
       </c>
       <c r="D5" t="n">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="E5" t="n">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="F5" t="n">
         <v>652</v>
       </c>
       <c r="G5" t="n">
-        <v>746</v>
+        <v>642</v>
       </c>
       <c r="H5" t="n">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="I5" t="n">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="J5" t="n">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="L5" t="n">
-        <v>686.2</v>
+        <v>671.2</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>581</v>
+        <v>665</v>
       </c>
       <c r="C6" t="n">
-        <v>567</v>
+        <v>519</v>
       </c>
       <c r="D6" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E6" t="n">
+        <v>542</v>
+      </c>
+      <c r="F6" t="n">
+        <v>632</v>
+      </c>
+      <c r="G6" t="n">
         <v>593</v>
       </c>
-      <c r="F6" t="n">
-        <v>647</v>
-      </c>
-      <c r="G6" t="n">
-        <v>579</v>
-      </c>
       <c r="H6" t="n">
+        <v>598</v>
+      </c>
+      <c r="I6" t="n">
+        <v>614</v>
+      </c>
+      <c r="J6" t="n">
+        <v>656</v>
+      </c>
+      <c r="K6" t="n">
         <v>594</v>
       </c>
-      <c r="I6" t="n">
-        <v>660</v>
-      </c>
-      <c r="J6" t="n">
-        <v>725</v>
-      </c>
-      <c r="K6" t="n">
-        <v>585</v>
-      </c>
       <c r="L6" t="n">
-        <v>616.4</v>
+        <v>604.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
+        <v>617</v>
+      </c>
+      <c r="C7" t="n">
+        <v>604</v>
+      </c>
+      <c r="D7" t="n">
+        <v>684</v>
+      </c>
+      <c r="E7" t="n">
+        <v>612</v>
+      </c>
+      <c r="F7" t="n">
+        <v>665</v>
+      </c>
+      <c r="G7" t="n">
+        <v>744</v>
+      </c>
+      <c r="H7" t="n">
+        <v>667</v>
+      </c>
+      <c r="I7" t="n">
         <v>638</v>
       </c>
-      <c r="C7" t="n">
-        <v>619</v>
-      </c>
-      <c r="D7" t="n">
-        <v>678</v>
-      </c>
-      <c r="E7" t="n">
-        <v>598</v>
-      </c>
-      <c r="F7" t="n">
-        <v>705</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
+        <v>525</v>
+      </c>
+      <c r="K7" t="n">
         <v>568</v>
       </c>
-      <c r="H7" t="n">
-        <v>565</v>
-      </c>
-      <c r="I7" t="n">
-        <v>617</v>
-      </c>
-      <c r="J7" t="n">
-        <v>620</v>
-      </c>
-      <c r="K7" t="n">
-        <v>639</v>
-      </c>
       <c r="L7" t="n">
-        <v>624.7</v>
+        <v>632.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>609</v>
+        <v>665</v>
       </c>
       <c r="C8" t="n">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="E8" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="F8" t="n">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="G8" t="n">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="H8" t="n">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="I8" t="n">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="J8" t="n">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="K8" t="n">
-        <v>660</v>
+        <v>596</v>
       </c>
       <c r="L8" t="n">
-        <v>598.2</v>
+        <v>607.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>632</v>
+        <v>535</v>
       </c>
       <c r="C9" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="D9" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E9" t="n">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="F9" t="n">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="G9" t="n">
-        <v>649</v>
+        <v>603</v>
       </c>
       <c r="H9" t="n">
-        <v>653</v>
+        <v>585</v>
       </c>
       <c r="I9" t="n">
-        <v>684</v>
+        <v>588</v>
       </c>
       <c r="J9" t="n">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="K9" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L9" t="n">
-        <v>623.3</v>
+        <v>594.8</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>805</v>
+        <v>702</v>
       </c>
       <c r="C10" t="n">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="D10" t="n">
-        <v>769</v>
+        <v>850</v>
       </c>
       <c r="E10" t="n">
-        <v>746</v>
+        <v>692</v>
       </c>
       <c r="F10" t="n">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="G10" t="n">
-        <v>671</v>
+        <v>694</v>
       </c>
       <c r="H10" t="n">
-        <v>644</v>
+        <v>801</v>
       </c>
       <c r="I10" t="n">
-        <v>805</v>
+        <v>777</v>
       </c>
       <c r="J10" t="n">
-        <v>725</v>
+        <v>831</v>
       </c>
       <c r="K10" t="n">
-        <v>672</v>
+        <v>758</v>
       </c>
       <c r="L10" t="n">
-        <v>726.9</v>
+        <v>754.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>582</v>
+        <v>747</v>
       </c>
       <c r="C11" t="n">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="D11" t="n">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="E11" t="n">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="F11" t="n">
-        <v>696</v>
+        <v>592</v>
       </c>
       <c r="G11" t="n">
-        <v>720</v>
+        <v>698</v>
       </c>
       <c r="H11" t="n">
-        <v>614</v>
+        <v>753</v>
       </c>
       <c r="I11" t="n">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="J11" t="n">
-        <v>555</v>
+        <v>673</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>689</v>
       </c>
       <c r="L11" t="n">
-        <v>638.5</v>
+        <v>683.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>682</v>
+        <v>764</v>
       </c>
       <c r="C12" t="n">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D12" t="n">
-        <v>655</v>
+        <v>629</v>
       </c>
       <c r="E12" t="n">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="F12" t="n">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="G12" t="n">
         <v>645</v>
       </c>
       <c r="H12" t="n">
-        <v>630</v>
+        <v>692</v>
       </c>
       <c r="I12" t="n">
-        <v>707</v>
+        <v>638</v>
       </c>
       <c r="J12" t="n">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="K12" t="n">
-        <v>690</v>
+        <v>629</v>
       </c>
       <c r="L12" t="n">
-        <v>660.7</v>
+        <v>663.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>781</v>
+        <v>852</v>
       </c>
       <c r="C13" t="n">
-        <v>823</v>
+        <v>750</v>
       </c>
       <c r="D13" t="n">
-        <v>716</v>
+        <v>692</v>
       </c>
       <c r="E13" t="n">
-        <v>883</v>
+        <v>773</v>
       </c>
       <c r="F13" t="n">
-        <v>778</v>
+        <v>737</v>
       </c>
       <c r="G13" t="n">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="H13" t="n">
-        <v>782</v>
+        <v>868</v>
       </c>
       <c r="I13" t="n">
-        <v>714</v>
+        <v>795</v>
       </c>
       <c r="J13" t="n">
-        <v>808</v>
+        <v>732</v>
       </c>
       <c r="K13" t="n">
-        <v>770</v>
+        <v>705</v>
       </c>
       <c r="L13" t="n">
-        <v>780.3</v>
+        <v>769.8</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>841</v>
+        <v>592</v>
       </c>
       <c r="C14" t="n">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D14" t="n">
-        <v>555</v>
+        <v>647</v>
       </c>
       <c r="E14" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="F14" t="n">
-        <v>671</v>
+        <v>735</v>
       </c>
       <c r="G14" t="n">
-        <v>842</v>
+        <v>665</v>
       </c>
       <c r="H14" t="n">
-        <v>688</v>
+        <v>636</v>
       </c>
       <c r="I14" t="n">
-        <v>764</v>
+        <v>653</v>
       </c>
       <c r="J14" t="n">
-        <v>698</v>
+        <v>664</v>
       </c>
       <c r="K14" t="n">
-        <v>799</v>
+        <v>622</v>
       </c>
       <c r="L14" t="n">
-        <v>722.8</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>654</v>
+        <v>678</v>
       </c>
       <c r="C15" t="n">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="D15" t="n">
-        <v>691</v>
+        <v>638</v>
       </c>
       <c r="E15" t="n">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="F15" t="n">
-        <v>802</v>
+        <v>662</v>
       </c>
       <c r="G15" t="n">
-        <v>804</v>
+        <v>664</v>
       </c>
       <c r="H15" t="n">
-        <v>695</v>
+        <v>577</v>
       </c>
       <c r="I15" t="n">
-        <v>736</v>
+        <v>616</v>
       </c>
       <c r="J15" t="n">
-        <v>741</v>
+        <v>630</v>
       </c>
       <c r="K15" t="n">
-        <v>664</v>
+        <v>549</v>
       </c>
       <c r="L15" t="n">
-        <v>717.1</v>
+        <v>642.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>729</v>
+        <v>640</v>
       </c>
       <c r="C16" t="n">
-        <v>701</v>
+        <v>666</v>
       </c>
       <c r="D16" t="n">
-        <v>585</v>
+        <v>631</v>
       </c>
       <c r="E16" t="n">
+        <v>615</v>
+      </c>
+      <c r="F16" t="n">
+        <v>675</v>
+      </c>
+      <c r="G16" t="n">
+        <v>700</v>
+      </c>
+      <c r="H16" t="n">
+        <v>589</v>
+      </c>
+      <c r="I16" t="n">
         <v>623</v>
       </c>
-      <c r="F16" t="n">
-        <v>621</v>
-      </c>
-      <c r="G16" t="n">
-        <v>696</v>
-      </c>
-      <c r="H16" t="n">
-        <v>604</v>
-      </c>
-      <c r="I16" t="n">
-        <v>619</v>
-      </c>
       <c r="J16" t="n">
-        <v>823</v>
+        <v>693</v>
       </c>
       <c r="K16" t="n">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="L16" t="n">
-        <v>663.9</v>
+        <v>650.6</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>619</v>
+        <v>542</v>
       </c>
       <c r="C17" t="n">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="D17" t="n">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="E17" t="n">
-        <v>662</v>
+        <v>609</v>
       </c>
       <c r="F17" t="n">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="G17" t="n">
-        <v>646</v>
+        <v>618</v>
       </c>
       <c r="H17" t="n">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="I17" t="n">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="J17" t="n">
-        <v>637</v>
+        <v>659</v>
       </c>
       <c r="K17" t="n">
-        <v>650</v>
+        <v>716</v>
       </c>
       <c r="L17" t="n">
-        <v>631.1</v>
+        <v>634.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>650</v>
+        <v>601</v>
       </c>
       <c r="C18" t="n">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="D18" t="n">
-        <v>693</v>
+        <v>757</v>
       </c>
       <c r="E18" t="n">
-        <v>738</v>
+        <v>762</v>
       </c>
       <c r="F18" t="n">
-        <v>596</v>
+        <v>757</v>
       </c>
       <c r="G18" t="n">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="H18" t="n">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="I18" t="n">
-        <v>783</v>
+        <v>697</v>
       </c>
       <c r="J18" t="n">
-        <v>689</v>
+        <v>804</v>
       </c>
       <c r="K18" t="n">
-        <v>645</v>
+        <v>747</v>
       </c>
       <c r="L18" t="n">
-        <v>697.4</v>
+        <v>729.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>751</v>
+        <v>691</v>
       </c>
       <c r="C19" t="n">
-        <v>666</v>
+        <v>757</v>
       </c>
       <c r="D19" t="n">
-        <v>696</v>
+        <v>672</v>
       </c>
       <c r="E19" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="F19" t="n">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="G19" t="n">
-        <v>732</v>
+        <v>695</v>
       </c>
       <c r="H19" t="n">
-        <v>778</v>
+        <v>612</v>
       </c>
       <c r="I19" t="n">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="J19" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="K19" t="n">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="L19" t="n">
-        <v>699.6</v>
+        <v>686.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
+        <v>921</v>
+      </c>
+      <c r="C20" t="n">
+        <v>750</v>
+      </c>
+      <c r="D20" t="n">
+        <v>780</v>
+      </c>
+      <c r="E20" t="n">
+        <v>848</v>
+      </c>
+      <c r="F20" t="n">
+        <v>738</v>
+      </c>
+      <c r="G20" t="n">
         <v>709</v>
       </c>
-      <c r="C20" t="n">
-        <v>906</v>
-      </c>
-      <c r="D20" t="n">
-        <v>706</v>
-      </c>
-      <c r="E20" t="n">
-        <v>721</v>
-      </c>
-      <c r="F20" t="n">
-        <v>783</v>
-      </c>
-      <c r="G20" t="n">
-        <v>698</v>
-      </c>
       <c r="H20" t="n">
-        <v>774</v>
+        <v>808</v>
       </c>
       <c r="I20" t="n">
-        <v>684</v>
+        <v>861</v>
       </c>
       <c r="J20" t="n">
-        <v>741</v>
+        <v>791</v>
       </c>
       <c r="K20" t="n">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="L20" t="n">
-        <v>741.6</v>
+        <v>788.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="C21" t="n">
-        <v>808</v>
+        <v>653</v>
       </c>
       <c r="D21" t="n">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="E21" t="n">
-        <v>752</v>
+        <v>589</v>
       </c>
       <c r="F21" t="n">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="G21" t="n">
-        <v>671</v>
+        <v>769</v>
       </c>
       <c r="H21" t="n">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I21" t="n">
-        <v>735</v>
+        <v>771</v>
       </c>
       <c r="J21" t="n">
-        <v>735</v>
+        <v>677</v>
       </c>
       <c r="K21" t="n">
-        <v>753</v>
+        <v>669</v>
       </c>
       <c r="L21" t="n">
-        <v>732.3</v>
+        <v>699.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C22" t="n">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="D22" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" t="n">
+        <v>608</v>
+      </c>
+      <c r="F22" t="n">
+        <v>634</v>
+      </c>
+      <c r="G22" t="n">
+        <v>588</v>
+      </c>
+      <c r="H22" t="n">
+        <v>706</v>
+      </c>
+      <c r="I22" t="n">
+        <v>678</v>
+      </c>
+      <c r="J22" t="n">
         <v>661</v>
       </c>
-      <c r="E22" t="n">
-        <v>609</v>
-      </c>
-      <c r="F22" t="n">
-        <v>598</v>
-      </c>
-      <c r="G22" t="n">
-        <v>593</v>
-      </c>
-      <c r="H22" t="n">
-        <v>638</v>
-      </c>
-      <c r="I22" t="n">
-        <v>701</v>
-      </c>
-      <c r="J22" t="n">
-        <v>696</v>
-      </c>
       <c r="K22" t="n">
-        <v>730</v>
+        <v>636</v>
       </c>
       <c r="L22" t="n">
-        <v>647.2</v>
+        <v>639.6</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>627</v>
+        <v>758</v>
       </c>
       <c r="C23" t="n">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="D23" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="E23" t="n">
-        <v>680</v>
+        <v>555</v>
       </c>
       <c r="F23" t="n">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="G23" t="n">
-        <v>592</v>
+        <v>737</v>
       </c>
       <c r="H23" t="n">
-        <v>663</v>
+        <v>602</v>
       </c>
       <c r="I23" t="n">
-        <v>681</v>
+        <v>641</v>
       </c>
       <c r="J23" t="n">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="K23" t="n">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="L23" t="n">
-        <v>630.3</v>
+        <v>644.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>610</v>
+        <v>696</v>
       </c>
       <c r="C24" t="n">
-        <v>794</v>
+        <v>681</v>
       </c>
       <c r="D24" t="n">
+        <v>739</v>
+      </c>
+      <c r="E24" t="n">
+        <v>654</v>
+      </c>
+      <c r="F24" t="n">
+        <v>745</v>
+      </c>
+      <c r="G24" t="n">
         <v>644</v>
       </c>
-      <c r="E24" t="n">
-        <v>734</v>
-      </c>
-      <c r="F24" t="n">
-        <v>729</v>
-      </c>
-      <c r="G24" t="n">
-        <v>764</v>
-      </c>
       <c r="H24" t="n">
-        <v>685</v>
+        <v>615</v>
       </c>
       <c r="I24" t="n">
-        <v>691</v>
+        <v>779</v>
       </c>
       <c r="J24" t="n">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="K24" t="n">
-        <v>639</v>
+        <v>723</v>
       </c>
       <c r="L24" t="n">
-        <v>702.6</v>
+        <v>701.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>700</v>
+        <v>599</v>
       </c>
       <c r="C25" t="n">
-        <v>699</v>
+        <v>578</v>
       </c>
       <c r="D25" t="n">
-        <v>700</v>
+        <v>661</v>
       </c>
       <c r="E25" t="n">
-        <v>651</v>
+        <v>564</v>
       </c>
       <c r="F25" t="n">
+        <v>671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>723</v>
+      </c>
+      <c r="H25" t="n">
+        <v>670</v>
+      </c>
+      <c r="I25" t="n">
+        <v>722</v>
+      </c>
+      <c r="J25" t="n">
         <v>686</v>
       </c>
-      <c r="G25" t="n">
-        <v>683</v>
-      </c>
-      <c r="H25" t="n">
-        <v>648</v>
-      </c>
-      <c r="I25" t="n">
-        <v>631</v>
-      </c>
-      <c r="J25" t="n">
-        <v>578</v>
-      </c>
       <c r="K25" t="n">
-        <v>851</v>
+        <v>583</v>
       </c>
       <c r="L25" t="n">
-        <v>682.7</v>
+        <v>645.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>633</v>
+        <v>733</v>
       </c>
       <c r="C26" t="n">
-        <v>614</v>
+        <v>708</v>
       </c>
       <c r="D26" t="n">
-        <v>596</v>
+        <v>699</v>
       </c>
       <c r="E26" t="n">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="F26" t="n">
-        <v>681</v>
+        <v>726</v>
       </c>
       <c r="G26" t="n">
-        <v>692</v>
+        <v>611</v>
       </c>
       <c r="H26" t="n">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="I26" t="n">
-        <v>594</v>
+        <v>738</v>
       </c>
       <c r="J26" t="n">
-        <v>628</v>
+        <v>690</v>
       </c>
       <c r="K26" t="n">
-        <v>680</v>
+        <v>625</v>
       </c>
       <c r="L26" t="n">
-        <v>654</v>
+        <v>691.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
+        <v>625</v>
+      </c>
+      <c r="C27" t="n">
+        <v>582</v>
+      </c>
+      <c r="D27" t="n">
         <v>523</v>
       </c>
-      <c r="C27" t="n">
-        <v>611</v>
-      </c>
-      <c r="D27" t="n">
-        <v>567</v>
-      </c>
       <c r="E27" t="n">
-        <v>571</v>
+        <v>604</v>
       </c>
       <c r="F27" t="n">
-        <v>523</v>
+        <v>615</v>
       </c>
       <c r="G27" t="n">
-        <v>527</v>
+        <v>605</v>
       </c>
       <c r="H27" t="n">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="I27" t="n">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="J27" t="n">
-        <v>588</v>
+        <v>702</v>
       </c>
       <c r="K27" t="n">
-        <v>656</v>
+        <v>689</v>
       </c>
       <c r="L27" t="n">
-        <v>582.3</v>
+        <v>620.8</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="C28" t="n">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="D28" t="n">
-        <v>635</v>
+        <v>699</v>
       </c>
       <c r="E28" t="n">
-        <v>745</v>
+        <v>599</v>
       </c>
       <c r="F28" t="n">
-        <v>721</v>
+        <v>614</v>
       </c>
       <c r="G28" t="n">
-        <v>665</v>
+        <v>736</v>
       </c>
       <c r="H28" t="n">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="I28" t="n">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="J28" t="n">
-        <v>692</v>
+        <v>639</v>
       </c>
       <c r="K28" t="n">
-        <v>663</v>
+        <v>594</v>
       </c>
       <c r="L28" t="n">
-        <v>669.6</v>
+        <v>646.3</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>729</v>
+        <v>644</v>
       </c>
       <c r="C29" t="n">
-        <v>705</v>
+        <v>643</v>
       </c>
       <c r="D29" t="n">
-        <v>714</v>
+        <v>644</v>
       </c>
       <c r="E29" t="n">
-        <v>578</v>
+        <v>666</v>
       </c>
       <c r="F29" t="n">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="G29" t="n">
-        <v>726</v>
+        <v>653</v>
       </c>
       <c r="H29" t="n">
-        <v>660</v>
+        <v>704</v>
       </c>
       <c r="I29" t="n">
-        <v>673</v>
+        <v>766</v>
       </c>
       <c r="J29" t="n">
-        <v>791</v>
+        <v>689</v>
       </c>
       <c r="K29" t="n">
-        <v>678</v>
+        <v>767</v>
       </c>
       <c r="L29" t="n">
-        <v>686</v>
+        <v>681.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C30" t="n">
-        <v>641</v>
+        <v>739</v>
       </c>
       <c r="D30" t="n">
+        <v>673</v>
+      </c>
+      <c r="E30" t="n">
+        <v>644</v>
+      </c>
+      <c r="F30" t="n">
+        <v>570</v>
+      </c>
+      <c r="G30" t="n">
+        <v>633</v>
+      </c>
+      <c r="H30" t="n">
+        <v>597</v>
+      </c>
+      <c r="I30" t="n">
+        <v>660</v>
+      </c>
+      <c r="J30" t="n">
         <v>610</v>
       </c>
-      <c r="E30" t="n">
-        <v>759</v>
-      </c>
-      <c r="F30" t="n">
-        <v>619</v>
-      </c>
-      <c r="G30" t="n">
-        <v>630</v>
-      </c>
-      <c r="H30" t="n">
-        <v>665</v>
-      </c>
-      <c r="I30" t="n">
-        <v>595</v>
-      </c>
-      <c r="J30" t="n">
-        <v>709</v>
-      </c>
       <c r="K30" t="n">
-        <v>722</v>
+        <v>620</v>
       </c>
       <c r="L30" t="n">
-        <v>658.4</v>
+        <v>638.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="C31" t="n">
-        <v>854</v>
+        <v>774</v>
       </c>
       <c r="D31" t="n">
-        <v>797</v>
+        <v>765</v>
       </c>
       <c r="E31" t="n">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="F31" t="n">
-        <v>645</v>
+        <v>747</v>
       </c>
       <c r="G31" t="n">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="H31" t="n">
-        <v>774</v>
+        <v>650</v>
       </c>
       <c r="I31" t="n">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="J31" t="n">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="K31" t="n">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="L31" t="n">
-        <v>734.5</v>
+        <v>724.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="C32" t="n">
-        <v>618</v>
+        <v>709</v>
       </c>
       <c r="D32" t="n">
-        <v>799</v>
+        <v>642</v>
       </c>
       <c r="E32" t="n">
-        <v>669</v>
+        <v>635</v>
       </c>
       <c r="F32" t="n">
-        <v>612</v>
+        <v>713</v>
       </c>
       <c r="G32" t="n">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="H32" t="n">
-        <v>635</v>
+        <v>716</v>
       </c>
       <c r="I32" t="n">
-        <v>730</v>
+        <v>650</v>
       </c>
       <c r="J32" t="n">
-        <v>713</v>
+        <v>622</v>
       </c>
       <c r="K32" t="n">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="L32" t="n">
-        <v>677.2</v>
+        <v>673.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>726</v>
+        <v>675</v>
       </c>
       <c r="C33" t="n">
+        <v>601</v>
+      </c>
+      <c r="D33" t="n">
+        <v>716</v>
+      </c>
+      <c r="E33" t="n">
+        <v>671</v>
+      </c>
+      <c r="F33" t="n">
+        <v>663</v>
+      </c>
+      <c r="G33" t="n">
+        <v>667</v>
+      </c>
+      <c r="H33" t="n">
+        <v>854</v>
+      </c>
+      <c r="I33" t="n">
+        <v>723</v>
+      </c>
+      <c r="J33" t="n">
         <v>684</v>
       </c>
-      <c r="D33" t="n">
-        <v>729</v>
-      </c>
-      <c r="E33" t="n">
-        <v>670</v>
-      </c>
-      <c r="F33" t="n">
-        <v>690</v>
-      </c>
-      <c r="G33" t="n">
-        <v>688</v>
-      </c>
-      <c r="H33" t="n">
-        <v>765</v>
-      </c>
-      <c r="I33" t="n">
-        <v>856</v>
-      </c>
-      <c r="J33" t="n">
-        <v>655</v>
-      </c>
       <c r="K33" t="n">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="L33" t="n">
-        <v>716.1</v>
+        <v>692.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>646</v>
+        <v>619</v>
       </c>
       <c r="C34" t="n">
+        <v>639</v>
+      </c>
+      <c r="D34" t="n">
+        <v>755</v>
+      </c>
+      <c r="E34" t="n">
+        <v>644</v>
+      </c>
+      <c r="F34" t="n">
+        <v>710</v>
+      </c>
+      <c r="G34" t="n">
         <v>595</v>
       </c>
-      <c r="D34" t="n">
-        <v>769</v>
-      </c>
-      <c r="E34" t="n">
-        <v>595</v>
-      </c>
-      <c r="F34" t="n">
-        <v>630</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
+        <v>621</v>
+      </c>
+      <c r="I34" t="n">
+        <v>760</v>
+      </c>
+      <c r="J34" t="n">
+        <v>620</v>
+      </c>
+      <c r="K34" t="n">
         <v>665</v>
       </c>
-      <c r="H34" t="n">
-        <v>637</v>
-      </c>
-      <c r="I34" t="n">
-        <v>756</v>
-      </c>
-      <c r="J34" t="n">
-        <v>689</v>
-      </c>
-      <c r="K34" t="n">
-        <v>664</v>
-      </c>
       <c r="L34" t="n">
-        <v>664.6</v>
+        <v>662.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>567</v>
+        <v>679</v>
       </c>
       <c r="C35" t="n">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="D35" t="n">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="E35" t="n">
-        <v>511</v>
+        <v>571</v>
       </c>
       <c r="F35" t="n">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="G35" t="n">
-        <v>558</v>
+        <v>621</v>
       </c>
       <c r="H35" t="n">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="I35" t="n">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J35" t="n">
-        <v>659</v>
+        <v>583</v>
       </c>
       <c r="K35" t="n">
-        <v>646</v>
+        <v>608</v>
       </c>
       <c r="L35" t="n">
-        <v>579.4</v>
+        <v>597.7</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>683</v>
+        <v>728</v>
       </c>
       <c r="C36" t="n">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="D36" t="n">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="E36" t="n">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="F36" t="n">
-        <v>763</v>
+        <v>658</v>
       </c>
       <c r="G36" t="n">
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="H36" t="n">
-        <v>656</v>
+        <v>741</v>
       </c>
       <c r="I36" t="n">
-        <v>589</v>
+        <v>774</v>
       </c>
       <c r="J36" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="K36" t="n">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="L36" t="n">
-        <v>649.6</v>
+        <v>676.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>804</v>
+        <v>708</v>
       </c>
       <c r="C37" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D37" t="n">
-        <v>799</v>
+        <v>595</v>
       </c>
       <c r="E37" t="n">
-        <v>637</v>
+        <v>760</v>
       </c>
       <c r="F37" t="n">
-        <v>738</v>
+        <v>794</v>
       </c>
       <c r="G37" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="H37" t="n">
-        <v>730</v>
+        <v>680</v>
       </c>
       <c r="I37" t="n">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="J37" t="n">
-        <v>737</v>
+        <v>627</v>
       </c>
       <c r="K37" t="n">
-        <v>869</v>
+        <v>580</v>
       </c>
       <c r="L37" t="n">
-        <v>734.4</v>
+        <v>680.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>543</v>
+        <v>672</v>
       </c>
       <c r="C38" t="n">
-        <v>652</v>
+        <v>602</v>
       </c>
       <c r="D38" t="n">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="E38" t="n">
+        <v>628</v>
+      </c>
+      <c r="F38" t="n">
+        <v>646</v>
+      </c>
+      <c r="G38" t="n">
+        <v>681</v>
+      </c>
+      <c r="H38" t="n">
+        <v>745</v>
+      </c>
+      <c r="I38" t="n">
         <v>618</v>
       </c>
-      <c r="F38" t="n">
-        <v>574</v>
-      </c>
-      <c r="G38" t="n">
-        <v>662</v>
-      </c>
-      <c r="H38" t="n">
-        <v>689</v>
-      </c>
-      <c r="I38" t="n">
-        <v>642</v>
-      </c>
       <c r="J38" t="n">
-        <v>661</v>
+        <v>538</v>
       </c>
       <c r="K38" t="n">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="L38" t="n">
-        <v>626</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>550</v>
+        <v>706</v>
       </c>
       <c r="C39" t="n">
-        <v>622</v>
+        <v>528</v>
       </c>
       <c r="D39" t="n">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E39" t="n">
-        <v>637</v>
+        <v>557</v>
       </c>
       <c r="F39" t="n">
-        <v>638</v>
+        <v>548</v>
       </c>
       <c r="G39" t="n">
-        <v>556</v>
+        <v>504</v>
       </c>
       <c r="H39" t="n">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="I39" t="n">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="J39" t="n">
-        <v>614</v>
+        <v>690</v>
       </c>
       <c r="K39" t="n">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L39" t="n">
-        <v>596.8</v>
+        <v>588.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>633</v>
+        <v>797</v>
       </c>
       <c r="C40" t="n">
-        <v>750</v>
+        <v>708</v>
       </c>
       <c r="D40" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E40" t="n">
-        <v>814</v>
+        <v>635</v>
       </c>
       <c r="F40" t="n">
-        <v>652</v>
+        <v>580</v>
       </c>
       <c r="G40" t="n">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="H40" t="n">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="I40" t="n">
-        <v>620</v>
+        <v>703</v>
       </c>
       <c r="J40" t="n">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="K40" t="n">
-        <v>749</v>
+        <v>663</v>
       </c>
       <c r="L40" t="n">
-        <v>692.5</v>
+        <v>679.3</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>601</v>
+        <v>644</v>
       </c>
       <c r="C41" t="n">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="D41" t="n">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="E41" t="n">
-        <v>706</v>
+        <v>591</v>
       </c>
       <c r="F41" t="n">
-        <v>684</v>
+        <v>645</v>
       </c>
       <c r="G41" t="n">
-        <v>622</v>
+        <v>546</v>
       </c>
       <c r="H41" t="n">
-        <v>623</v>
+        <v>716</v>
       </c>
       <c r="I41" t="n">
-        <v>621</v>
+        <v>674</v>
       </c>
       <c r="J41" t="n">
-        <v>711</v>
+        <v>639</v>
       </c>
       <c r="K41" t="n">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="L41" t="n">
-        <v>641.4</v>
+        <v>629.7</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="C42" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D42" t="n">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="E42" t="n">
-        <v>739</v>
+        <v>629</v>
       </c>
       <c r="F42" t="n">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="G42" t="n">
-        <v>725</v>
+        <v>809</v>
       </c>
       <c r="H42" t="n">
-        <v>715</v>
+        <v>772</v>
       </c>
       <c r="I42" t="n">
-        <v>634</v>
+        <v>755</v>
       </c>
       <c r="J42" t="n">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="K42" t="n">
-        <v>705</v>
+        <v>791</v>
       </c>
       <c r="L42" t="n">
-        <v>699.8</v>
+        <v>733.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>797</v>
+        <v>706</v>
       </c>
       <c r="C43" t="n">
-        <v>671</v>
+        <v>822</v>
       </c>
       <c r="D43" t="n">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="E43" t="n">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F43" t="n">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="G43" t="n">
-        <v>800</v>
+        <v>715</v>
       </c>
       <c r="H43" t="n">
-        <v>694</v>
+        <v>837</v>
       </c>
       <c r="I43" t="n">
-        <v>741</v>
+        <v>785</v>
       </c>
       <c r="J43" t="n">
-        <v>725</v>
+        <v>588</v>
       </c>
       <c r="K43" t="n">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="L43" t="n">
-        <v>728</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="C44" t="n">
-        <v>632</v>
+        <v>689</v>
       </c>
       <c r="D44" t="n">
-        <v>785</v>
+        <v>637</v>
       </c>
       <c r="E44" t="n">
-        <v>701</v>
+        <v>600</v>
       </c>
       <c r="F44" t="n">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G44" t="n">
-        <v>594</v>
+        <v>674</v>
       </c>
       <c r="H44" t="n">
-        <v>581</v>
+        <v>675</v>
       </c>
       <c r="I44" t="n">
-        <v>729</v>
+        <v>642</v>
       </c>
       <c r="J44" t="n">
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="K44" t="n">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="L44" t="n">
-        <v>651.8</v>
+        <v>643.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>629</v>
+        <v>671</v>
       </c>
       <c r="C45" t="n">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D45" t="n">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="E45" t="n">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="F45" t="n">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="G45" t="n">
-        <v>676</v>
+        <v>758</v>
       </c>
       <c r="H45" t="n">
-        <v>717</v>
+        <v>647</v>
       </c>
       <c r="I45" t="n">
-        <v>794</v>
+        <v>686</v>
       </c>
       <c r="J45" t="n">
-        <v>716</v>
+        <v>692</v>
       </c>
       <c r="K45" t="n">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="L45" t="n">
-        <v>689.2</v>
+        <v>678</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="C46" t="n">
-        <v>635</v>
+        <v>668</v>
       </c>
       <c r="D46" t="n">
-        <v>612</v>
+        <v>574</v>
       </c>
       <c r="E46" t="n">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="F46" t="n">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="G46" t="n">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="H46" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="I46" t="n">
-        <v>634</v>
+        <v>699</v>
       </c>
       <c r="J46" t="n">
-        <v>583</v>
+        <v>632</v>
       </c>
       <c r="K46" t="n">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="L46" t="n">
-        <v>646.2</v>
+        <v>655.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>769</v>
+        <v>663</v>
       </c>
       <c r="C47" t="n">
-        <v>569</v>
+        <v>706</v>
       </c>
       <c r="D47" t="n">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E47" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F47" t="n">
-        <v>562</v>
+        <v>671</v>
       </c>
       <c r="G47" t="n">
-        <v>538</v>
+        <v>650</v>
       </c>
       <c r="H47" t="n">
-        <v>703</v>
+        <v>625</v>
       </c>
       <c r="I47" t="n">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="J47" t="n">
-        <v>681</v>
+        <v>629</v>
       </c>
       <c r="K47" t="n">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="L47" t="n">
-        <v>643.7</v>
+        <v>653.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="C48" t="n">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D48" t="n">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E48" t="n">
+        <v>688</v>
+      </c>
+      <c r="F48" t="n">
+        <v>786</v>
+      </c>
+      <c r="G48" t="n">
+        <v>800</v>
+      </c>
+      <c r="H48" t="n">
+        <v>750</v>
+      </c>
+      <c r="I48" t="n">
         <v>662</v>
       </c>
-      <c r="F48" t="n">
-        <v>759</v>
-      </c>
-      <c r="G48" t="n">
-        <v>824</v>
-      </c>
-      <c r="H48" t="n">
-        <v>695</v>
-      </c>
-      <c r="I48" t="n">
-        <v>674</v>
-      </c>
       <c r="J48" t="n">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="K48" t="n">
-        <v>826</v>
+        <v>761</v>
       </c>
       <c r="L48" t="n">
-        <v>743.1</v>
+        <v>747.6</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>692</v>
+        <v>760</v>
       </c>
       <c r="C49" t="n">
-        <v>670</v>
+        <v>723</v>
       </c>
       <c r="D49" t="n">
-        <v>738</v>
+        <v>831</v>
       </c>
       <c r="E49" t="n">
-        <v>729</v>
+        <v>775</v>
       </c>
       <c r="F49" t="n">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="G49" t="n">
-        <v>690</v>
+        <v>856</v>
       </c>
       <c r="H49" t="n">
-        <v>857</v>
+        <v>686</v>
       </c>
       <c r="I49" t="n">
-        <v>776</v>
+        <v>704</v>
       </c>
       <c r="J49" t="n">
-        <v>765</v>
+        <v>672</v>
       </c>
       <c r="K49" t="n">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="L49" t="n">
-        <v>728.8</v>
+        <v>741.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>631</v>
+        <v>552</v>
       </c>
       <c r="C50" t="n">
-        <v>614</v>
+        <v>689</v>
       </c>
       <c r="D50" t="n">
-        <v>693</v>
+        <v>759</v>
       </c>
       <c r="E50" t="n">
-        <v>674</v>
+        <v>627</v>
       </c>
       <c r="F50" t="n">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="G50" t="n">
-        <v>644</v>
+        <v>709</v>
       </c>
       <c r="H50" t="n">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="I50" t="n">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="J50" t="n">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="K50" t="n">
-        <v>631</v>
+        <v>730</v>
       </c>
       <c r="L50" t="n">
-        <v>647.4</v>
+        <v>673</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>570</v>
+        <v>647</v>
       </c>
       <c r="C51" t="n">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="D51" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E51" t="n">
-        <v>648</v>
+        <v>701</v>
       </c>
       <c r="F51" t="n">
-        <v>621</v>
+        <v>734</v>
       </c>
       <c r="G51" t="n">
-        <v>739</v>
+        <v>652</v>
       </c>
       <c r="H51" t="n">
-        <v>604</v>
+        <v>728</v>
       </c>
       <c r="I51" t="n">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="J51" t="n">
-        <v>716</v>
+        <v>645</v>
       </c>
       <c r="K51" t="n">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="L51" t="n">
-        <v>657.4</v>
+        <v>676.6</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>667.98</v>
+        <v>674.2</v>
       </c>
       <c r="C52" t="n">
-        <v>663.8200000000001</v>
+        <v>668.88</v>
       </c>
       <c r="D52" t="n">
-        <v>673.66</v>
+        <v>671.02</v>
       </c>
       <c r="E52" t="n">
-        <v>674.04</v>
+        <v>654.52</v>
       </c>
       <c r="F52" t="n">
-        <v>664.6</v>
+        <v>668.8</v>
       </c>
       <c r="G52" t="n">
-        <v>670.04</v>
+        <v>671.98</v>
       </c>
       <c r="H52" t="n">
-        <v>668.3</v>
+        <v>680.16</v>
       </c>
       <c r="I52" t="n">
-        <v>671.9400000000001</v>
+        <v>676.6</v>
       </c>
       <c r="J52" t="n">
-        <v>675.9400000000001</v>
+        <v>664.36</v>
       </c>
       <c r="K52" t="n">
-        <v>670.62</v>
+        <v>656.6</v>
       </c>
       <c r="L52" t="n">
-        <v>670.0940000000001</v>
+        <v>668.7120000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.99232006072998</v>
+        <v>6.653087615966797</v>
       </c>
       <c r="C2" t="n">
-        <v>4.106049537658691</v>
+        <v>5.646013975143433</v>
       </c>
       <c r="D2" t="n">
-        <v>5.342413902282715</v>
+        <v>4.988253355026245</v>
       </c>
       <c r="E2" t="n">
-        <v>4.566859722137451</v>
+        <v>4.215289831161499</v>
       </c>
       <c r="F2" t="n">
-        <v>4.253671169281006</v>
+        <v>6.132815837860107</v>
       </c>
       <c r="G2" t="n">
-        <v>4.241207122802734</v>
+        <v>4.201912403106689</v>
       </c>
       <c r="H2" t="n">
-        <v>3.997836112976074</v>
+        <v>4.714704036712646</v>
       </c>
       <c r="I2" t="n">
-        <v>3.977451086044312</v>
+        <v>5.540674924850464</v>
       </c>
       <c r="J2" t="n">
-        <v>3.917021512985229</v>
+        <v>5.339132070541382</v>
       </c>
       <c r="K2" t="n">
-        <v>3.942452669143677</v>
+        <v>4.724436044692993</v>
       </c>
       <c r="L2" t="n">
-        <v>4.233728289604187</v>
+        <v>5.215632009506225</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.075132608413696</v>
+        <v>5.406801462173462</v>
       </c>
       <c r="C3" t="n">
-        <v>4.071630001068115</v>
+        <v>5.779720306396484</v>
       </c>
       <c r="D3" t="n">
-        <v>4.563405275344849</v>
+        <v>5.326825141906738</v>
       </c>
       <c r="E3" t="n">
-        <v>4.752388477325439</v>
+        <v>6.114699125289917</v>
       </c>
       <c r="F3" t="n">
-        <v>5.668102025985718</v>
+        <v>5.359524488449097</v>
       </c>
       <c r="G3" t="n">
-        <v>4.162888765335083</v>
+        <v>4.662912368774414</v>
       </c>
       <c r="H3" t="n">
-        <v>4.447168350219727</v>
+        <v>7.134616374969482</v>
       </c>
       <c r="I3" t="n">
-        <v>4.202780961990356</v>
+        <v>4.445439577102661</v>
       </c>
       <c r="J3" t="n">
-        <v>3.864657163619995</v>
+        <v>5.760602235794067</v>
       </c>
       <c r="K3" t="n">
-        <v>4.346430063247681</v>
+        <v>5.102717638015747</v>
       </c>
       <c r="L3" t="n">
-        <v>4.415458369255066</v>
+        <v>5.509385871887207</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.023273468017578</v>
+        <v>3.96734356880188</v>
       </c>
       <c r="C4" t="n">
-        <v>3.482109546661377</v>
+        <v>5.509904384613037</v>
       </c>
       <c r="D4" t="n">
-        <v>3.753466367721558</v>
+        <v>3.714847326278687</v>
       </c>
       <c r="E4" t="n">
-        <v>3.563407421112061</v>
+        <v>4.020155191421509</v>
       </c>
       <c r="F4" t="n">
-        <v>3.428760766983032</v>
+        <v>4.179147481918335</v>
       </c>
       <c r="G4" t="n">
-        <v>3.544469118118286</v>
+        <v>5.27081036567688</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65767502784729</v>
+        <v>4.458440780639648</v>
       </c>
       <c r="I4" t="n">
-        <v>3.520515203475952</v>
+        <v>3.898154258728027</v>
       </c>
       <c r="J4" t="n">
-        <v>3.684129953384399</v>
+        <v>4.124085903167725</v>
       </c>
       <c r="K4" t="n">
-        <v>3.494605541229248</v>
+        <v>4.336377620697021</v>
       </c>
       <c r="L4" t="n">
-        <v>3.615241241455078</v>
+        <v>4.347926688194275</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>3.828271150588989</v>
+        <v>4.664519548416138</v>
       </c>
       <c r="C5" t="n">
-        <v>3.707065343856812</v>
+        <v>4.279892921447754</v>
       </c>
       <c r="D5" t="n">
-        <v>4.586326599121094</v>
+        <v>4.564507246017456</v>
       </c>
       <c r="E5" t="n">
-        <v>3.767890214920044</v>
+        <v>4.83251953125</v>
       </c>
       <c r="F5" t="n">
-        <v>3.733767032623291</v>
+        <v>4.231543302536011</v>
       </c>
       <c r="G5" t="n">
-        <v>4.374617576599121</v>
+        <v>5.869004011154175</v>
       </c>
       <c r="H5" t="n">
-        <v>3.999093055725098</v>
+        <v>4.892045259475708</v>
       </c>
       <c r="I5" t="n">
-        <v>3.880409717559814</v>
+        <v>4.178405284881592</v>
       </c>
       <c r="J5" t="n">
-        <v>3.815081596374512</v>
+        <v>4.771530151367188</v>
       </c>
       <c r="K5" t="n">
-        <v>3.775181293487549</v>
+        <v>4.969918012619019</v>
       </c>
       <c r="L5" t="n">
-        <v>3.946770358085632</v>
+        <v>4.725388526916504</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.71684193611145</v>
+        <v>4.68240761756897</v>
       </c>
       <c r="C6" t="n">
-        <v>3.739782094955444</v>
+        <v>4.659510135650635</v>
       </c>
       <c r="D6" t="n">
-        <v>4.049951076507568</v>
+        <v>5.310104131698608</v>
       </c>
       <c r="E6" t="n">
-        <v>3.760711908340454</v>
+        <v>4.434422254562378</v>
       </c>
       <c r="F6" t="n">
-        <v>3.971664428710938</v>
+        <v>6.02245306968689</v>
       </c>
       <c r="G6" t="n">
-        <v>3.741773128509521</v>
+        <v>4.067536354064941</v>
       </c>
       <c r="H6" t="n">
-        <v>3.986631870269775</v>
+        <v>5.110027074813843</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840004444122314</v>
+        <v>5.841040134429932</v>
       </c>
       <c r="J6" t="n">
-        <v>4.920705318450928</v>
+        <v>5.326862096786499</v>
       </c>
       <c r="K6" t="n">
-        <v>4.039993286132812</v>
+        <v>4.360624074935913</v>
       </c>
       <c r="L6" t="n">
-        <v>3.976805949211121</v>
+        <v>4.98149869441986</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.57120680809021</v>
+        <v>5.305698871612549</v>
       </c>
       <c r="C7" t="n">
-        <v>3.792138814926147</v>
+        <v>4.597445487976074</v>
       </c>
       <c r="D7" t="n">
-        <v>3.562746047973633</v>
+        <v>4.821327209472656</v>
       </c>
       <c r="E7" t="n">
-        <v>3.778661727905273</v>
+        <v>5.096124410629272</v>
       </c>
       <c r="F7" t="n">
-        <v>4.18411660194397</v>
+        <v>4.678646802902222</v>
       </c>
       <c r="G7" t="n">
-        <v>3.733840703964233</v>
+        <v>4.585936307907104</v>
       </c>
       <c r="H7" t="n">
-        <v>3.791126251220703</v>
+        <v>5.799457311630249</v>
       </c>
       <c r="I7" t="n">
-        <v>3.64600944519043</v>
+        <v>4.765590906143188</v>
       </c>
       <c r="J7" t="n">
-        <v>3.692419767379761</v>
+        <v>4.461259365081787</v>
       </c>
       <c r="K7" t="n">
-        <v>3.641020059585571</v>
+        <v>6.754637241363525</v>
       </c>
       <c r="L7" t="n">
-        <v>3.739328622817993</v>
+        <v>5.086612391471863</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.935260772705078</v>
+        <v>4.718517065048218</v>
       </c>
       <c r="C8" t="n">
-        <v>4.116836547851562</v>
+        <v>4.471401453018188</v>
       </c>
       <c r="D8" t="n">
-        <v>3.88301157951355</v>
+        <v>5.210566520690918</v>
       </c>
       <c r="E8" t="n">
-        <v>4.183355093002319</v>
+        <v>4.774158239364624</v>
       </c>
       <c r="F8" t="n">
-        <v>3.978346586227417</v>
+        <v>4.626780271530151</v>
       </c>
       <c r="G8" t="n">
-        <v>3.933011054992676</v>
+        <v>5.809033393859863</v>
       </c>
       <c r="H8" t="n">
-        <v>3.877116441726685</v>
+        <v>4.531504154205322</v>
       </c>
       <c r="I8" t="n">
-        <v>3.529515266418457</v>
+        <v>4.638331174850464</v>
       </c>
       <c r="J8" t="n">
-        <v>3.739484310150146</v>
+        <v>4.956836223602295</v>
       </c>
       <c r="K8" t="n">
-        <v>4.064630746841431</v>
+        <v>4.631558895111084</v>
       </c>
       <c r="L8" t="n">
-        <v>3.924056839942932</v>
+        <v>4.836868739128112</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.445762872695923</v>
+        <v>4.115541458129883</v>
       </c>
       <c r="C9" t="n">
-        <v>3.251705646514893</v>
+        <v>5.246562957763672</v>
       </c>
       <c r="D9" t="n">
-        <v>3.457690477371216</v>
+        <v>4.190128326416016</v>
       </c>
       <c r="E9" t="n">
-        <v>3.412289381027222</v>
+        <v>4.156857967376709</v>
       </c>
       <c r="F9" t="n">
-        <v>3.642710208892822</v>
+        <v>3.868484973907471</v>
       </c>
       <c r="G9" t="n">
-        <v>3.496586322784424</v>
+        <v>4.905829191207886</v>
       </c>
       <c r="H9" t="n">
-        <v>3.436245203018188</v>
+        <v>4.034720897674561</v>
       </c>
       <c r="I9" t="n">
-        <v>4.624245405197144</v>
+        <v>3.837860822677612</v>
       </c>
       <c r="J9" t="n">
-        <v>4.043213367462158</v>
+        <v>5.059847593307495</v>
       </c>
       <c r="K9" t="n">
-        <v>3.362924098968506</v>
+        <v>4.217056512832642</v>
       </c>
       <c r="L9" t="n">
-        <v>3.61733729839325</v>
+        <v>4.363289070129395</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.006261110305786</v>
+        <v>4.927255630493164</v>
       </c>
       <c r="C10" t="n">
-        <v>5.034694910049438</v>
+        <v>5.734264850616455</v>
       </c>
       <c r="D10" t="n">
-        <v>5.186286687850952</v>
+        <v>6.118329524993896</v>
       </c>
       <c r="E10" t="n">
-        <v>4.633193016052246</v>
+        <v>5.477068901062012</v>
       </c>
       <c r="F10" t="n">
-        <v>4.641686677932739</v>
+        <v>5.497071504592896</v>
       </c>
       <c r="G10" t="n">
-        <v>4.408796548843384</v>
+        <v>5.512919664382935</v>
       </c>
       <c r="H10" t="n">
-        <v>4.632179737091064</v>
+        <v>5.240039825439453</v>
       </c>
       <c r="I10" t="n">
-        <v>5.528422117233276</v>
+        <v>5.525310039520264</v>
       </c>
       <c r="J10" t="n">
-        <v>5.310963869094849</v>
+        <v>5.158978700637817</v>
       </c>
       <c r="K10" t="n">
-        <v>4.989290475845337</v>
+        <v>6.23738956451416</v>
       </c>
       <c r="L10" t="n">
-        <v>4.937177515029907</v>
+        <v>5.542862820625305</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.241198778152466</v>
+        <v>5.213499784469604</v>
       </c>
       <c r="C11" t="n">
-        <v>4.240691184997559</v>
+        <v>5.891557455062866</v>
       </c>
       <c r="D11" t="n">
-        <v>4.214288949966431</v>
+        <v>5.294634342193604</v>
       </c>
       <c r="E11" t="n">
-        <v>5.207735300064087</v>
+        <v>4.967062950134277</v>
       </c>
       <c r="F11" t="n">
-        <v>4.252156496047974</v>
+        <v>4.434451341629028</v>
       </c>
       <c r="G11" t="n">
-        <v>4.091067790985107</v>
+        <v>4.272382974624634</v>
       </c>
       <c r="H11" t="n">
-        <v>4.230228424072266</v>
+        <v>4.952613592147827</v>
       </c>
       <c r="I11" t="n">
-        <v>4.106053113937378</v>
+        <v>4.093847751617432</v>
       </c>
       <c r="J11" t="n">
-        <v>4.69758129119873</v>
+        <v>4.942645072937012</v>
       </c>
       <c r="K11" t="n">
-        <v>4.333456516265869</v>
+        <v>4.963086605072021</v>
       </c>
       <c r="L11" t="n">
-        <v>4.361445784568787</v>
+        <v>4.902578186988831</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.827249050140381</v>
+        <v>4.458910226821899</v>
       </c>
       <c r="C12" t="n">
-        <v>3.686111211776733</v>
+        <v>3.746770620346069</v>
       </c>
       <c r="D12" t="n">
-        <v>4.387842893600464</v>
+        <v>3.715831279754639</v>
       </c>
       <c r="E12" t="n">
-        <v>3.80232572555542</v>
+        <v>4.094866275787354</v>
       </c>
       <c r="F12" t="n">
-        <v>4.57786226272583</v>
+        <v>3.857462406158447</v>
       </c>
       <c r="G12" t="n">
-        <v>3.597872734069824</v>
+        <v>3.979151725769043</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85349440574646</v>
+        <v>4.086904525756836</v>
       </c>
       <c r="I12" t="n">
-        <v>3.912311315536499</v>
+        <v>3.776192665100098</v>
       </c>
       <c r="J12" t="n">
-        <v>3.711843252182007</v>
+        <v>3.907328367233276</v>
       </c>
       <c r="K12" t="n">
-        <v>3.76770281791687</v>
+        <v>3.738759279251099</v>
       </c>
       <c r="L12" t="n">
-        <v>3.912461566925049</v>
+        <v>3.936217737197876</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.364548683166504</v>
+        <v>5.254838466644287</v>
       </c>
       <c r="C13" t="n">
-        <v>5.565514087677002</v>
+        <v>4.792031764984131</v>
       </c>
       <c r="D13" t="n">
-        <v>4.228052854537964</v>
+        <v>4.826962947845459</v>
       </c>
       <c r="E13" t="n">
-        <v>5.598466873168945</v>
+        <v>4.982571363449097</v>
       </c>
       <c r="F13" t="n">
-        <v>4.874326705932617</v>
+        <v>4.967072725296021</v>
       </c>
       <c r="G13" t="n">
-        <v>4.801507234573364</v>
+        <v>4.344193696975708</v>
       </c>
       <c r="H13" t="n">
-        <v>5.093242406845093</v>
+        <v>4.768605709075928</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9970383644104</v>
+        <v>5.078290462493896</v>
       </c>
       <c r="J13" t="n">
-        <v>5.335260391235352</v>
+        <v>5.118197202682495</v>
       </c>
       <c r="K13" t="n">
-        <v>4.683583498001099</v>
+        <v>4.43145751953125</v>
       </c>
       <c r="L13" t="n">
-        <v>5.054154109954834</v>
+        <v>4.856422185897827</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>5.654841661453247</v>
+        <v>4.003576755523682</v>
       </c>
       <c r="C14" t="n">
-        <v>4.280352830886841</v>
+        <v>4.057447910308838</v>
       </c>
       <c r="D14" t="n">
-        <v>3.809300184249878</v>
+        <v>4.003574848175049</v>
       </c>
       <c r="E14" t="n">
-        <v>3.819267272949219</v>
+        <v>4.181118249893188</v>
       </c>
       <c r="F14" t="n">
-        <v>4.500036001205444</v>
+        <v>4.678332090377808</v>
       </c>
       <c r="G14" t="n">
-        <v>5.160067319869995</v>
+        <v>4.14406418800354</v>
       </c>
       <c r="H14" t="n">
-        <v>4.491065740585327</v>
+        <v>3.875628232955933</v>
       </c>
       <c r="I14" t="n">
-        <v>4.649158000946045</v>
+        <v>3.943446397781372</v>
       </c>
       <c r="J14" t="n">
-        <v>4.071144580841064</v>
+        <v>3.894571781158447</v>
       </c>
       <c r="K14" t="n">
-        <v>4.375841379165649</v>
+        <v>4.177356719970703</v>
       </c>
       <c r="L14" t="n">
-        <v>4.481107497215271</v>
+        <v>4.095911717414856</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.820236444473267</v>
+        <v>4.815740585327148</v>
       </c>
       <c r="C15" t="n">
-        <v>4.809749364852905</v>
+        <v>4.734943389892578</v>
       </c>
       <c r="D15" t="n">
-        <v>4.715495586395264</v>
+        <v>4.27916693687439</v>
       </c>
       <c r="E15" t="n">
-        <v>4.300032377243042</v>
+        <v>4.762333631515503</v>
       </c>
       <c r="F15" t="n">
-        <v>5.147379159927368</v>
+        <v>4.664101600646973</v>
       </c>
       <c r="G15" t="n">
-        <v>4.704509973526001</v>
+        <v>4.577329397201538</v>
       </c>
       <c r="H15" t="n">
-        <v>4.611258745193481</v>
+        <v>4.181346893310547</v>
       </c>
       <c r="I15" t="n">
-        <v>4.391836404800415</v>
+        <v>3.914543151855469</v>
       </c>
       <c r="J15" t="n">
-        <v>4.39857816696167</v>
+        <v>4.341463088989258</v>
       </c>
       <c r="K15" t="n">
-        <v>4.37261438369751</v>
+        <v>4.017765998840332</v>
       </c>
       <c r="L15" t="n">
-        <v>4.627169060707092</v>
+        <v>4.428873467445373</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.317289590835571</v>
+        <v>4.153411149978638</v>
       </c>
       <c r="C16" t="n">
-        <v>4.072903871536255</v>
+        <v>4.044682741165161</v>
       </c>
       <c r="D16" t="n">
-        <v>4.107881546020508</v>
+        <v>4.09807276725769</v>
       </c>
       <c r="E16" t="n">
-        <v>4.105826377868652</v>
+        <v>4.147932529449463</v>
       </c>
       <c r="F16" t="n">
-        <v>4.147706747055054</v>
+        <v>4.025260210037231</v>
       </c>
       <c r="G16" t="n">
-        <v>3.981635570526123</v>
+        <v>4.432703256607056</v>
       </c>
       <c r="H16" t="n">
-        <v>3.911355257034302</v>
+        <v>4.031733274459839</v>
       </c>
       <c r="I16" t="n">
-        <v>4.364136695861816</v>
+        <v>4.007824659347534</v>
       </c>
       <c r="J16" t="n">
-        <v>4.530227661132812</v>
+        <v>4.120988845825195</v>
       </c>
       <c r="K16" t="n">
-        <v>3.891884326934814</v>
+        <v>3.988828420639038</v>
       </c>
       <c r="L16" t="n">
-        <v>4.143084764480591</v>
+        <v>4.105143785476685</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.374126672744751</v>
+        <v>3.704068660736084</v>
       </c>
       <c r="C17" t="n">
-        <v>4.081256628036499</v>
+        <v>4.036713838577271</v>
       </c>
       <c r="D17" t="n">
-        <v>4.685587882995605</v>
+        <v>4.290581703186035</v>
       </c>
       <c r="E17" t="n">
-        <v>4.01177191734314</v>
+        <v>4.213279485702515</v>
       </c>
       <c r="F17" t="n">
-        <v>4.330471277236938</v>
+        <v>4.59030294418335</v>
       </c>
       <c r="G17" t="n">
-        <v>3.891596078872681</v>
+        <v>4.264656782150269</v>
       </c>
       <c r="H17" t="n">
-        <v>4.254158973693848</v>
+        <v>4.023780822753906</v>
       </c>
       <c r="I17" t="n">
-        <v>4.109050035476685</v>
+        <v>4.336483716964722</v>
       </c>
       <c r="J17" t="n">
-        <v>4.412768840789795</v>
+        <v>4.189327955245972</v>
       </c>
       <c r="K17" t="n">
-        <v>3.961931943893433</v>
+        <v>4.660132646560669</v>
       </c>
       <c r="L17" t="n">
-        <v>4.211272025108338</v>
+        <v>4.230932855606079</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.199302911758423</v>
+        <v>4.038228988647461</v>
       </c>
       <c r="C18" t="n">
-        <v>4.434718370437622</v>
+        <v>4.266121387481689</v>
       </c>
       <c r="D18" t="n">
-        <v>4.423737764358521</v>
+        <v>4.153413772583008</v>
       </c>
       <c r="E18" t="n">
-        <v>4.586355686187744</v>
+        <v>4.445669889450073</v>
       </c>
       <c r="F18" t="n">
-        <v>4.140993356704712</v>
+        <v>4.52099871635437</v>
       </c>
       <c r="G18" t="n">
-        <v>4.112007141113281</v>
+        <v>5.193798303604126</v>
       </c>
       <c r="H18" t="n">
-        <v>5.152870178222656</v>
+        <v>4.309514045715332</v>
       </c>
       <c r="I18" t="n">
-        <v>5.207724094390869</v>
+        <v>4.491077661514282</v>
       </c>
       <c r="J18" t="n">
-        <v>4.176848649978638</v>
+        <v>4.725444316864014</v>
       </c>
       <c r="K18" t="n">
-        <v>4.241722106933594</v>
+        <v>4.26912260055542</v>
       </c>
       <c r="L18" t="n">
-        <v>4.467628026008606</v>
+        <v>4.441338968276978</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.163882970809937</v>
+        <v>4.556894302368164</v>
       </c>
       <c r="C19" t="n">
-        <v>4.453182458877563</v>
+        <v>4.503026247024536</v>
       </c>
       <c r="D19" t="n">
-        <v>4.183816909790039</v>
+        <v>4.081151485443115</v>
       </c>
       <c r="E19" t="n">
-        <v>3.934995412826538</v>
+        <v>4.387091398239136</v>
       </c>
       <c r="F19" t="n">
-        <v>4.396285057067871</v>
+        <v>4.155200004577637</v>
       </c>
       <c r="G19" t="n">
-        <v>4.087094306945801</v>
+        <v>4.351211786270142</v>
       </c>
       <c r="H19" t="n">
-        <v>4.769853353500366</v>
+        <v>3.953765153884888</v>
       </c>
       <c r="I19" t="n">
-        <v>3.768890619277954</v>
+        <v>3.996598720550537</v>
       </c>
       <c r="J19" t="n">
-        <v>4.035236358642578</v>
+        <v>3.874927520751953</v>
       </c>
       <c r="K19" t="n">
-        <v>4.014796018600464</v>
+        <v>5.087840557098389</v>
       </c>
       <c r="L19" t="n">
-        <v>4.180803346633911</v>
+        <v>4.29477071762085</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.864596128463745</v>
+        <v>5.987431764602661</v>
       </c>
       <c r="C20" t="n">
-        <v>5.399308204650879</v>
+        <v>4.687349557876587</v>
       </c>
       <c r="D20" t="n">
-        <v>4.454168796539307</v>
+        <v>5.618365526199341</v>
       </c>
       <c r="E20" t="n">
-        <v>4.932932615280151</v>
+        <v>4.947620391845703</v>
       </c>
       <c r="F20" t="n">
-        <v>4.842656850814819</v>
+        <v>4.940168619155884</v>
       </c>
       <c r="G20" t="n">
-        <v>4.729456901550293</v>
+        <v>4.750149488449097</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3987877368927</v>
+        <v>5.419889450073242</v>
       </c>
       <c r="I20" t="n">
-        <v>4.327480792999268</v>
+        <v>4.898772239685059</v>
       </c>
       <c r="J20" t="n">
-        <v>4.425724744796753</v>
+        <v>4.8553626537323</v>
       </c>
       <c r="K20" t="n">
-        <v>4.421271800994873</v>
+        <v>4.634478807449341</v>
       </c>
       <c r="L20" t="n">
-        <v>4.679638457298279</v>
+        <v>5.073958849906921</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.043693065643311</v>
+        <v>4.546666860580444</v>
       </c>
       <c r="C21" t="n">
-        <v>5.069606065750122</v>
+        <v>4.473894596099854</v>
       </c>
       <c r="D21" t="n">
-        <v>4.356412410736084</v>
+        <v>4.449418783187866</v>
       </c>
       <c r="E21" t="n">
-        <v>4.73842716217041</v>
+        <v>3.820066452026367</v>
       </c>
       <c r="F21" t="n">
-        <v>4.280590534210205</v>
+        <v>4.43349289894104</v>
       </c>
       <c r="G21" t="n">
-        <v>4.018749475479126</v>
+        <v>4.288342714309692</v>
       </c>
       <c r="H21" t="n">
-        <v>4.434707641601562</v>
+        <v>5.186734199523926</v>
       </c>
       <c r="I21" t="n">
-        <v>4.323492288589478</v>
+        <v>4.910970449447632</v>
       </c>
       <c r="J21" t="n">
-        <v>4.650656223297119</v>
+        <v>4.651172161102295</v>
       </c>
       <c r="K21" t="n">
-        <v>4.243193864822388</v>
+        <v>3.630253314971924</v>
       </c>
       <c r="L21" t="n">
-        <v>4.415952873229981</v>
+        <v>4.439101243019104</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.153439998626709</v>
+        <v>4.090085506439209</v>
       </c>
       <c r="C22" t="n">
-        <v>4.37834906578064</v>
+        <v>4.243203639984131</v>
       </c>
       <c r="D22" t="n">
-        <v>4.437216997146606</v>
+        <v>4.122999906539917</v>
       </c>
       <c r="E22" t="n">
-        <v>4.183838844299316</v>
+        <v>4.429725170135498</v>
       </c>
       <c r="F22" t="n">
-        <v>4.161407947540283</v>
+        <v>4.281605243682861</v>
       </c>
       <c r="G22" t="n">
-        <v>3.746951103210449</v>
+        <v>5.006280660629272</v>
       </c>
       <c r="H22" t="n">
-        <v>4.063183784484863</v>
+        <v>4.544928073883057</v>
       </c>
       <c r="I22" t="n">
-        <v>5.069072008132935</v>
+        <v>4.712483167648315</v>
       </c>
       <c r="J22" t="n">
-        <v>5.283040285110474</v>
+        <v>4.403818607330322</v>
       </c>
       <c r="K22" t="n">
-        <v>4.688558101654053</v>
+        <v>4.577338695526123</v>
       </c>
       <c r="L22" t="n">
-        <v>4.416505813598633</v>
+        <v>4.441246867179871</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.375876903533936</v>
+        <v>4.550885200500488</v>
       </c>
       <c r="C23" t="n">
-        <v>4.335453033447266</v>
+        <v>4.415753364562988</v>
       </c>
       <c r="D23" t="n">
-        <v>3.996869325637817</v>
+        <v>3.992864847183228</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0277259349823</v>
+        <v>4.018770217895508</v>
       </c>
       <c r="F23" t="n">
-        <v>3.939456939697266</v>
+        <v>3.971876621246338</v>
       </c>
       <c r="G23" t="n">
-        <v>3.835237979888916</v>
+        <v>4.26562762260437</v>
       </c>
       <c r="H23" t="n">
-        <v>4.242768526077271</v>
+        <v>3.77488112449646</v>
       </c>
       <c r="I23" t="n">
-        <v>4.176632642745972</v>
+        <v>3.934002876281738</v>
       </c>
       <c r="J23" t="n">
-        <v>3.902343273162842</v>
+        <v>4.005301475524902</v>
       </c>
       <c r="K23" t="n">
-        <v>4.014542102813721</v>
+        <v>4.341514110565186</v>
       </c>
       <c r="L23" t="n">
-        <v>4.08469066619873</v>
+        <v>4.127147746086121</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.227027177810669</v>
+        <v>4.363420248031616</v>
       </c>
       <c r="C24" t="n">
-        <v>4.945620059967041</v>
+        <v>4.299540042877197</v>
       </c>
       <c r="D24" t="n">
-        <v>4.08686089515686</v>
+        <v>4.403767585754395</v>
       </c>
       <c r="E24" t="n">
-        <v>4.358161926269531</v>
+        <v>4.612252235412598</v>
       </c>
       <c r="F24" t="n">
-        <v>4.4668869972229</v>
+        <v>4.570362091064453</v>
       </c>
       <c r="G24" t="n">
-        <v>4.244966745376587</v>
+        <v>4.244173288345337</v>
       </c>
       <c r="H24" t="n">
-        <v>4.889821290969849</v>
+        <v>4.288586616516113</v>
       </c>
       <c r="I24" t="n">
-        <v>5.211504459381104</v>
+        <v>4.870108604431152</v>
       </c>
       <c r="J24" t="n">
-        <v>5.267826795578003</v>
+        <v>4.581820487976074</v>
       </c>
       <c r="K24" t="n">
-        <v>4.314274787902832</v>
+        <v>4.709498643875122</v>
       </c>
       <c r="L24" t="n">
-        <v>4.601295113563538</v>
+        <v>4.494352984428406</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.757118701934814</v>
+        <v>4.133486270904541</v>
       </c>
       <c r="C25" t="n">
-        <v>4.377632856369019</v>
+        <v>3.871155023574829</v>
       </c>
       <c r="D25" t="n">
-        <v>4.294333696365356</v>
+        <v>4.138465404510498</v>
       </c>
       <c r="E25" t="n">
-        <v>4.118778705596924</v>
+        <v>4.098548173904419</v>
       </c>
       <c r="F25" t="n">
-        <v>4.657884359359741</v>
+        <v>4.118529558181763</v>
       </c>
       <c r="G25" t="n">
-        <v>4.313284635543823</v>
+        <v>4.653167486190796</v>
       </c>
       <c r="H25" t="n">
-        <v>4.351685762405396</v>
+        <v>3.973883390426636</v>
       </c>
       <c r="I25" t="n">
-        <v>4.250951528549194</v>
+        <v>5.05013108253479</v>
       </c>
       <c r="J25" t="n">
-        <v>3.889388799667358</v>
+        <v>4.26764965057373</v>
       </c>
       <c r="K25" t="n">
-        <v>5.356582641601562</v>
+        <v>4.32548999786377</v>
       </c>
       <c r="L25" t="n">
-        <v>4.436764168739319</v>
+        <v>4.263050603866577</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.152189016342163</v>
+        <v>5.024213314056396</v>
       </c>
       <c r="C26" t="n">
-        <v>4.293356418609619</v>
+        <v>4.136956930160522</v>
       </c>
       <c r="D26" t="n">
-        <v>4.154697179794312</v>
+        <v>4.514498233795166</v>
       </c>
       <c r="E26" t="n">
-        <v>4.47287917137146</v>
+        <v>4.217260837554932</v>
       </c>
       <c r="F26" t="n">
-        <v>4.427494764328003</v>
+        <v>4.071609020233154</v>
       </c>
       <c r="G26" t="n">
-        <v>4.031504154205322</v>
+        <v>3.99381422996521</v>
       </c>
       <c r="H26" t="n">
-        <v>4.098853826522827</v>
+        <v>4.418753385543823</v>
       </c>
       <c r="I26" t="n">
-        <v>4.441459894180298</v>
+        <v>4.622211694717407</v>
       </c>
       <c r="J26" t="n">
-        <v>4.102837562561035</v>
+        <v>4.07613468170166</v>
       </c>
       <c r="K26" t="n">
-        <v>4.034009456634521</v>
+        <v>4.30951452255249</v>
       </c>
       <c r="L26" t="n">
-        <v>4.220928144454956</v>
+        <v>4.338496685028076</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.910317182540894</v>
+        <v>4.420135021209717</v>
       </c>
       <c r="C27" t="n">
-        <v>3.860948801040649</v>
+        <v>3.84849214553833</v>
       </c>
       <c r="D27" t="n">
-        <v>3.706842184066772</v>
+        <v>3.716841459274292</v>
       </c>
       <c r="E27" t="n">
-        <v>3.893368005752563</v>
+        <v>4.248970031738281</v>
       </c>
       <c r="F27" t="n">
-        <v>3.955218076705933</v>
+        <v>4.05383825302124</v>
       </c>
       <c r="G27" t="n">
-        <v>3.952372550964355</v>
+        <v>4.22675085067749</v>
       </c>
       <c r="H27" t="n">
-        <v>4.031507968902588</v>
+        <v>4.621241092681885</v>
       </c>
       <c r="I27" t="n">
-        <v>4.152692794799805</v>
+        <v>4.450039148330688</v>
       </c>
       <c r="J27" t="n">
-        <v>4.00159478187561</v>
+        <v>4.4354567527771</v>
       </c>
       <c r="K27" t="n">
-        <v>4.184109687805176</v>
+        <v>4.402094841003418</v>
       </c>
       <c r="L27" t="n">
-        <v>3.964897203445434</v>
+        <v>4.242385959625244</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>3.57671856880188</v>
+        <v>3.795331716537476</v>
       </c>
       <c r="C28" t="n">
-        <v>3.907333374023438</v>
+        <v>3.834744691848755</v>
       </c>
       <c r="D28" t="n">
-        <v>3.910327434539795</v>
+        <v>4.230224609375</v>
       </c>
       <c r="E28" t="n">
-        <v>4.26439380645752</v>
+        <v>3.709074974060059</v>
       </c>
       <c r="F28" t="n">
-        <v>4.305793762207031</v>
+        <v>4.450668573379517</v>
       </c>
       <c r="G28" t="n">
-        <v>3.929785251617432</v>
+        <v>5.115495920181274</v>
       </c>
       <c r="H28" t="n">
-        <v>3.763717412948608</v>
+        <v>4.133498430252075</v>
       </c>
       <c r="I28" t="n">
-        <v>3.707841396331787</v>
+        <v>4.56688404083252</v>
       </c>
       <c r="J28" t="n">
-        <v>4.072923898696899</v>
+        <v>3.745954751968384</v>
       </c>
       <c r="K28" t="n">
-        <v>4.030522346496582</v>
+        <v>3.922338485717773</v>
       </c>
       <c r="L28" t="n">
-        <v>3.946935725212097</v>
+        <v>4.150421619415283</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.377644777297974</v>
+        <v>4.006494998931885</v>
       </c>
       <c r="C29" t="n">
-        <v>4.263925075531006</v>
+        <v>4.057674407958984</v>
       </c>
       <c r="D29" t="n">
-        <v>3.884389162063599</v>
+        <v>3.841715335845947</v>
       </c>
       <c r="E29" t="n">
-        <v>3.832022428512573</v>
+        <v>4.483559608459473</v>
       </c>
       <c r="F29" t="n">
-        <v>4.004584789276123</v>
+        <v>3.808285713195801</v>
       </c>
       <c r="G29" t="n">
-        <v>4.055930852890015</v>
+        <v>3.914525508880615</v>
       </c>
       <c r="H29" t="n">
-        <v>4.333242416381836</v>
+        <v>4.179367303848267</v>
       </c>
       <c r="I29" t="n">
-        <v>4.495803833007812</v>
+        <v>4.880082130432129</v>
       </c>
       <c r="J29" t="n">
-        <v>4.310285329818726</v>
+        <v>4.401778936386108</v>
       </c>
       <c r="K29" t="n">
-        <v>4.651924848556519</v>
+        <v>4.812736511230469</v>
       </c>
       <c r="L29" t="n">
-        <v>4.220975351333618</v>
+        <v>4.238622045516967</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.005589246749878</v>
+        <v>4.20530891418457</v>
       </c>
       <c r="C30" t="n">
-        <v>3.757238149642944</v>
+        <v>4.942949056625366</v>
       </c>
       <c r="D30" t="n">
-        <v>4.233010292053223</v>
+        <v>4.619272232055664</v>
       </c>
       <c r="E30" t="n">
-        <v>4.685326099395752</v>
+        <v>3.956932544708252</v>
       </c>
       <c r="F30" t="n">
-        <v>3.741793155670166</v>
+        <v>3.730011940002441</v>
       </c>
       <c r="G30" t="n">
-        <v>3.701868772506714</v>
+        <v>3.958416223526001</v>
       </c>
       <c r="H30" t="n">
-        <v>3.792129993438721</v>
+        <v>4.082097053527832</v>
       </c>
       <c r="I30" t="n">
-        <v>3.988627195358276</v>
+        <v>4.443676471710205</v>
       </c>
       <c r="J30" t="n">
-        <v>4.072420120239258</v>
+        <v>5.084586143493652</v>
       </c>
       <c r="K30" t="n">
-        <v>4.221018075942993</v>
+        <v>3.934262990951538</v>
       </c>
       <c r="L30" t="n">
-        <v>4.019902110099792</v>
+        <v>4.295751357078553</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.2818443775177</v>
+        <v>4.424989938735962</v>
       </c>
       <c r="C31" t="n">
-        <v>4.639423608779907</v>
+        <v>4.710251092910767</v>
       </c>
       <c r="D31" t="n">
-        <v>4.041470289230347</v>
+        <v>4.493327617645264</v>
       </c>
       <c r="E31" t="n">
-        <v>4.385586261749268</v>
+        <v>5.004969835281372</v>
       </c>
       <c r="F31" t="n">
-        <v>4.200561761856079</v>
+        <v>4.51573920249939</v>
       </c>
       <c r="G31" t="n">
-        <v>4.5401930809021</v>
+        <v>4.803539276123047</v>
       </c>
       <c r="H31" t="n">
-        <v>5.012959003448486</v>
+        <v>4.362651348114014</v>
       </c>
       <c r="I31" t="n">
-        <v>4.565642118453979</v>
+        <v>5.795986890792847</v>
       </c>
       <c r="J31" t="n">
-        <v>4.432011365890503</v>
+        <v>4.691296100616455</v>
       </c>
       <c r="K31" t="n">
-        <v>4.026537656784058</v>
+        <v>4.632948637008667</v>
       </c>
       <c r="L31" t="n">
-        <v>4.412622952461243</v>
+        <v>4.743569993972779</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.265901803970337</v>
+        <v>4.813470602035522</v>
       </c>
       <c r="C32" t="n">
-        <v>4.251458406448364</v>
+        <v>5.408954620361328</v>
       </c>
       <c r="D32" t="n">
-        <v>5.037908554077148</v>
+        <v>4.311306238174438</v>
       </c>
       <c r="E32" t="n">
-        <v>4.34620189666748</v>
+        <v>4.201076030731201</v>
       </c>
       <c r="F32" t="n">
-        <v>4.296315670013428</v>
+        <v>4.674813032150269</v>
       </c>
       <c r="G32" t="n">
-        <v>4.187118053436279</v>
+        <v>4.328757524490356</v>
       </c>
       <c r="H32" t="n">
-        <v>4.112790107727051</v>
+        <v>4.463405132293701</v>
       </c>
       <c r="I32" t="n">
-        <v>4.863845109939575</v>
+        <v>4.775576114654541</v>
       </c>
       <c r="J32" t="n">
-        <v>4.698769807815552</v>
+        <v>4.448428392410278</v>
       </c>
       <c r="K32" t="n">
-        <v>4.190107822418213</v>
+        <v>4.976065874099731</v>
       </c>
       <c r="L32" t="n">
-        <v>4.425041723251343</v>
+        <v>4.640185356140137</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.579108476638794</v>
+        <v>4.193178415298462</v>
       </c>
       <c r="C33" t="n">
-        <v>4.347184896469116</v>
+        <v>4.298338651657104</v>
       </c>
       <c r="D33" t="n">
-        <v>4.598045825958252</v>
+        <v>4.551676511764526</v>
       </c>
       <c r="E33" t="n">
-        <v>4.213036775588989</v>
+        <v>4.318264961242676</v>
       </c>
       <c r="F33" t="n">
-        <v>4.383594751358032</v>
+        <v>4.418525218963623</v>
       </c>
       <c r="G33" t="n">
-        <v>4.021523475646973</v>
+        <v>4.549187898635864</v>
       </c>
       <c r="H33" t="n">
-        <v>4.58607292175293</v>
+        <v>4.850369930267334</v>
       </c>
       <c r="I33" t="n">
-        <v>4.538684606552124</v>
+        <v>5.116183757781982</v>
       </c>
       <c r="J33" t="n">
-        <v>4.15817403793335</v>
+        <v>4.333212375640869</v>
       </c>
       <c r="K33" t="n">
-        <v>4.294854879379272</v>
+        <v>4.171144008636475</v>
       </c>
       <c r="L33" t="n">
-        <v>4.372028064727783</v>
+        <v>4.480008172988891</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.141262054443359</v>
+        <v>3.662970304489136</v>
       </c>
       <c r="C34" t="n">
-        <v>3.737780332565308</v>
+        <v>3.666455268859863</v>
       </c>
       <c r="D34" t="n">
-        <v>4.015543699264526</v>
+        <v>4.376692056655884</v>
       </c>
       <c r="E34" t="n">
-        <v>3.599654674530029</v>
+        <v>4.004571437835693</v>
       </c>
       <c r="F34" t="n">
-        <v>3.766259908676147</v>
+        <v>3.640527248382568</v>
       </c>
       <c r="G34" t="n">
-        <v>4.190638780593872</v>
+        <v>3.506385087966919</v>
       </c>
       <c r="H34" t="n">
-        <v>4.036007404327393</v>
+        <v>3.691895484924316</v>
       </c>
       <c r="I34" t="n">
-        <v>4.224019765853882</v>
+        <v>4.093842506408691</v>
       </c>
       <c r="J34" t="n">
-        <v>3.545275926589966</v>
+        <v>3.664461135864258</v>
       </c>
       <c r="K34" t="n">
-        <v>3.910343408584595</v>
+        <v>3.929802417755127</v>
       </c>
       <c r="L34" t="n">
-        <v>3.916678595542908</v>
+        <v>3.823760294914246</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>3.665962219238281</v>
+        <v>3.6505286693573</v>
       </c>
       <c r="C35" t="n">
-        <v>3.439058065414429</v>
+        <v>3.553762674331665</v>
       </c>
       <c r="D35" t="n">
-        <v>3.780168294906616</v>
+        <v>3.898366212844849</v>
       </c>
       <c r="E35" t="n">
-        <v>3.323840856552124</v>
+        <v>3.642355442047119</v>
       </c>
       <c r="F35" t="n">
-        <v>3.516345739364624</v>
+        <v>3.542605876922607</v>
       </c>
       <c r="G35" t="n">
-        <v>3.729800939559937</v>
+        <v>3.789361000061035</v>
       </c>
       <c r="H35" t="n">
-        <v>3.382211446762085</v>
+        <v>3.610799789428711</v>
       </c>
       <c r="I35" t="n">
-        <v>3.43804407119751</v>
+        <v>3.690120220184326</v>
       </c>
       <c r="J35" t="n">
-        <v>4.147216081619263</v>
+        <v>3.474655151367188</v>
       </c>
       <c r="K35" t="n">
-        <v>3.740758657455444</v>
+        <v>3.310078144073486</v>
       </c>
       <c r="L35" t="n">
-        <v>3.616340637207031</v>
+        <v>3.616263318061828</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.29333758354187</v>
+        <v>4.513006925582886</v>
       </c>
       <c r="C36" t="n">
-        <v>3.98464298248291</v>
+        <v>4.287582397460938</v>
       </c>
       <c r="D36" t="n">
-        <v>4.279879093170166</v>
+        <v>3.9085533618927</v>
       </c>
       <c r="E36" t="n">
-        <v>4.098842620849609</v>
+        <v>4.181837797164917</v>
       </c>
       <c r="F36" t="n">
-        <v>4.264405727386475</v>
+        <v>4.479087591171265</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03550386428833</v>
+        <v>3.982847929000854</v>
       </c>
       <c r="H36" t="n">
-        <v>4.086864948272705</v>
+        <v>4.239210367202759</v>
       </c>
       <c r="I36" t="n">
-        <v>3.712842702865601</v>
+        <v>4.268659114837646</v>
       </c>
       <c r="J36" t="n">
-        <v>3.929294109344482</v>
+        <v>3.921521425247192</v>
       </c>
       <c r="K36" t="n">
-        <v>3.955291748046875</v>
+        <v>3.984344005584717</v>
       </c>
       <c r="L36" t="n">
-        <v>4.064090538024902</v>
+        <v>4.176665091514588</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.087040662765503</v>
+        <v>4.737447261810303</v>
       </c>
       <c r="C37" t="n">
-        <v>4.415746212005615</v>
+        <v>4.621237516403198</v>
       </c>
       <c r="D37" t="n">
-        <v>4.521491050720215</v>
+        <v>4.894068241119385</v>
       </c>
       <c r="E37" t="n">
-        <v>4.40426230430603</v>
+        <v>5.445113182067871</v>
       </c>
       <c r="F37" t="n">
-        <v>5.087527990341187</v>
+        <v>5.378359317779541</v>
       </c>
       <c r="G37" t="n">
-        <v>5.52443265914917</v>
+        <v>4.922951936721802</v>
       </c>
       <c r="H37" t="n">
-        <v>4.887046575546265</v>
+        <v>4.85263466835022</v>
       </c>
       <c r="I37" t="n">
-        <v>5.093535184860229</v>
+        <v>4.482078790664673</v>
       </c>
       <c r="J37" t="n">
-        <v>4.954861879348755</v>
+        <v>4.589318990707397</v>
       </c>
       <c r="K37" t="n">
-        <v>5.656106233596802</v>
+        <v>4.432698488235474</v>
       </c>
       <c r="L37" t="n">
-        <v>4.963205075263977</v>
+        <v>4.835590839385986</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.640225172042847</v>
+        <v>3.83821439743042</v>
       </c>
       <c r="C38" t="n">
-        <v>3.5764000415802</v>
+        <v>3.692094564437866</v>
       </c>
       <c r="D38" t="n">
-        <v>3.771389961242676</v>
+        <v>3.646222352981567</v>
       </c>
       <c r="E38" t="n">
-        <v>3.670152902603149</v>
+        <v>3.86713433265686</v>
       </c>
       <c r="F38" t="n">
-        <v>3.536485910415649</v>
+        <v>3.861663579940796</v>
       </c>
       <c r="G38" t="n">
-        <v>3.601841449737549</v>
+        <v>3.869157075881958</v>
       </c>
       <c r="H38" t="n">
-        <v>3.850206613540649</v>
+        <v>4.316509246826172</v>
       </c>
       <c r="I38" t="n">
-        <v>3.582877635955811</v>
+        <v>3.691691637039185</v>
       </c>
       <c r="J38" t="n">
-        <v>3.944452047348022</v>
+        <v>3.482630252838135</v>
       </c>
       <c r="K38" t="n">
-        <v>3.928035497665405</v>
+        <v>3.90154767036438</v>
       </c>
       <c r="L38" t="n">
-        <v>3.710206723213196</v>
+        <v>3.816686511039734</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.717031002044678</v>
+        <v>4.238212823867798</v>
       </c>
       <c r="C39" t="n">
-        <v>4.016781806945801</v>
+        <v>3.84370231628418</v>
       </c>
       <c r="D39" t="n">
-        <v>4.008800745010376</v>
+        <v>4.238217353820801</v>
       </c>
       <c r="E39" t="n">
-        <v>4.167884349822998</v>
+        <v>4.216263294219971</v>
       </c>
       <c r="F39" t="n">
-        <v>4.25670862197876</v>
+        <v>4.005803823471069</v>
       </c>
       <c r="G39" t="n">
-        <v>3.912545919418335</v>
+        <v>3.814276933670044</v>
       </c>
       <c r="H39" t="n">
-        <v>4.082130670547485</v>
+        <v>3.795324802398682</v>
       </c>
       <c r="I39" t="n">
-        <v>4.146932601928711</v>
+        <v>3.845192432403564</v>
       </c>
       <c r="J39" t="n">
-        <v>3.925500869750977</v>
+        <v>4.662647008895874</v>
       </c>
       <c r="K39" t="n">
-        <v>3.982868671417236</v>
+        <v>3.728994369506836</v>
       </c>
       <c r="L39" t="n">
-        <v>4.021718525886536</v>
+        <v>4.038863515853881</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.029735088348389</v>
+        <v>5.537409067153931</v>
       </c>
       <c r="C40" t="n">
-        <v>4.924955129623413</v>
+        <v>4.79278302192688</v>
       </c>
       <c r="D40" t="n">
-        <v>4.358911037445068</v>
+        <v>4.081154108047485</v>
       </c>
       <c r="E40" t="n">
-        <v>5.570328712463379</v>
+        <v>4.485090017318726</v>
       </c>
       <c r="F40" t="n">
-        <v>4.310539484024048</v>
+        <v>4.024744033813477</v>
       </c>
       <c r="G40" t="n">
-        <v>4.266648292541504</v>
+        <v>4.503048181533813</v>
       </c>
       <c r="H40" t="n">
-        <v>5.52747368812561</v>
+        <v>5.020244598388672</v>
       </c>
       <c r="I40" t="n">
-        <v>4.762902021408081</v>
+        <v>4.418740749359131</v>
       </c>
       <c r="J40" t="n">
-        <v>4.671097040176392</v>
+        <v>4.38121771812439</v>
       </c>
       <c r="K40" t="n">
-        <v>4.909034252166748</v>
+        <v>4.475338459014893</v>
       </c>
       <c r="L40" t="n">
-        <v>4.733162474632263</v>
+        <v>4.571976995468139</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>3.841214895248413</v>
+        <v>4.140233278274536</v>
       </c>
       <c r="C41" t="n">
-        <v>4.030232429504395</v>
+        <v>3.966179370880127</v>
       </c>
       <c r="D41" t="n">
-        <v>3.751929759979248</v>
+        <v>3.991618633270264</v>
       </c>
       <c r="E41" t="n">
-        <v>4.067161798477173</v>
+        <v>4.013556003570557</v>
       </c>
       <c r="F41" t="n">
-        <v>4.379334688186646</v>
+        <v>4.267423868179321</v>
       </c>
       <c r="G41" t="n">
-        <v>4.030247449874878</v>
+        <v>3.894375324249268</v>
       </c>
       <c r="H41" t="n">
-        <v>4.194797992706299</v>
+        <v>4.540674448013306</v>
       </c>
       <c r="I41" t="n">
-        <v>4.260701656341553</v>
+        <v>4.182149887084961</v>
       </c>
       <c r="J41" t="n">
-        <v>3.970546007156372</v>
+        <v>4.195140361785889</v>
       </c>
       <c r="K41" t="n">
-        <v>3.86744499206543</v>
+        <v>3.961188316345215</v>
       </c>
       <c r="L41" t="n">
-        <v>4.03936116695404</v>
+        <v>4.115253949165345</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.525729894638062</v>
+        <v>5.17955756187439</v>
       </c>
       <c r="C42" t="n">
-        <v>4.194120168685913</v>
+        <v>4.575598239898682</v>
       </c>
       <c r="D42" t="n">
-        <v>4.158174753189087</v>
+        <v>5.299744367599487</v>
       </c>
       <c r="E42" t="n">
-        <v>4.423495531082153</v>
+        <v>4.237486124038696</v>
       </c>
       <c r="F42" t="n">
-        <v>4.848381757736206</v>
+        <v>5.018954753875732</v>
       </c>
       <c r="G42" t="n">
-        <v>4.362659692764282</v>
+        <v>4.936639308929443</v>
       </c>
       <c r="H42" t="n">
-        <v>4.492331743240356</v>
+        <v>4.897783994674683</v>
       </c>
       <c r="I42" t="n">
-        <v>4.17712664604187</v>
+        <v>4.876829385757446</v>
       </c>
       <c r="J42" t="n">
-        <v>4.385588407516479</v>
+        <v>4.651168584823608</v>
       </c>
       <c r="K42" t="n">
-        <v>4.213034868240356</v>
+        <v>5.545392513275146</v>
       </c>
       <c r="L42" t="n">
-        <v>4.378064346313477</v>
+        <v>4.921915483474732</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.329237699508667</v>
+        <v>4.143440008163452</v>
       </c>
       <c r="C43" t="n">
-        <v>4.355734348297119</v>
+        <v>5.245649337768555</v>
       </c>
       <c r="D43" t="n">
-        <v>5.845782279968262</v>
+        <v>4.739456653594971</v>
       </c>
       <c r="E43" t="n">
-        <v>4.42749547958374</v>
+        <v>4.386832475662231</v>
       </c>
       <c r="F43" t="n">
-        <v>4.25676155090332</v>
+        <v>4.070123434066772</v>
       </c>
       <c r="G43" t="n">
-        <v>5.002750158309937</v>
+        <v>4.527962446212769</v>
       </c>
       <c r="H43" t="n">
-        <v>4.071126461029053</v>
+        <v>4.516979694366455</v>
       </c>
       <c r="I43" t="n">
-        <v>4.828710079193115</v>
+        <v>4.786808252334595</v>
       </c>
       <c r="J43" t="n">
-        <v>4.481097936630249</v>
+        <v>4.18082332611084</v>
       </c>
       <c r="K43" t="n">
-        <v>4.050699949264526</v>
+        <v>4.265621900558472</v>
       </c>
       <c r="L43" t="n">
-        <v>4.564939594268798</v>
+        <v>4.486369752883911</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.029240608215332</v>
+        <v>4.493078708648682</v>
       </c>
       <c r="C44" t="n">
-        <v>4.2112877368927</v>
+        <v>4.051678419113159</v>
       </c>
       <c r="D44" t="n">
-        <v>5.10151219367981</v>
+        <v>3.967904567718506</v>
       </c>
       <c r="E44" t="n">
-        <v>4.124980211257935</v>
+        <v>4.142960071563721</v>
       </c>
       <c r="F44" t="n">
-        <v>4.648181676864624</v>
+        <v>4.177366256713867</v>
       </c>
       <c r="G44" t="n">
-        <v>4.015770435333252</v>
+        <v>3.98987603187561</v>
       </c>
       <c r="H44" t="n">
-        <v>4.160426616668701</v>
+        <v>4.189291715621948</v>
       </c>
       <c r="I44" t="n">
-        <v>4.416762351989746</v>
+        <v>3.822265863418579</v>
       </c>
       <c r="J44" t="n">
-        <v>3.701076745986938</v>
+        <v>4.199302434921265</v>
       </c>
       <c r="K44" t="n">
-        <v>4.370381832122803</v>
+        <v>4.027742385864258</v>
       </c>
       <c r="L44" t="n">
-        <v>4.277962040901184</v>
+        <v>4.10614664554596</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.540994167327881</v>
+        <v>3.718055725097656</v>
       </c>
       <c r="C45" t="n">
-        <v>3.947443008422852</v>
+        <v>3.988839387893677</v>
       </c>
       <c r="D45" t="n">
-        <v>3.726010084152222</v>
+        <v>3.64771556854248</v>
       </c>
       <c r="E45" t="n">
-        <v>3.593848943710327</v>
+        <v>3.794351816177368</v>
       </c>
       <c r="F45" t="n">
-        <v>4.308542013168335</v>
+        <v>3.916516065597534</v>
       </c>
       <c r="G45" t="n">
-        <v>3.904552936553955</v>
+        <v>4.029748916625977</v>
       </c>
       <c r="H45" t="n">
-        <v>4.062156677246094</v>
+        <v>4.05717396736145</v>
       </c>
       <c r="I45" t="n">
-        <v>4.277085065841675</v>
+        <v>3.812298774719238</v>
       </c>
       <c r="J45" t="n">
-        <v>4.186346054077148</v>
+        <v>3.854183197021484</v>
       </c>
       <c r="K45" t="n">
-        <v>3.952443361282349</v>
+        <v>3.668152570724487</v>
       </c>
       <c r="L45" t="n">
-        <v>3.949942231178284</v>
+        <v>3.848703598976135</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.206301927566528</v>
+        <v>4.192319631576538</v>
       </c>
       <c r="C46" t="n">
-        <v>3.967932939529419</v>
+        <v>4.206312656402588</v>
       </c>
       <c r="D46" t="n">
-        <v>4.063161373138428</v>
+        <v>4.05666446685791</v>
       </c>
       <c r="E46" t="n">
-        <v>4.131967544555664</v>
+        <v>4.752931118011475</v>
       </c>
       <c r="F46" t="n">
-        <v>4.334463596343994</v>
+        <v>4.128007411956787</v>
       </c>
       <c r="G46" t="n">
-        <v>4.499038457870483</v>
+        <v>4.67758846282959</v>
       </c>
       <c r="H46" t="n">
-        <v>3.891579627990723</v>
+        <v>4.255163908004761</v>
       </c>
       <c r="I46" t="n">
-        <v>3.972573518753052</v>
+        <v>4.346940279006958</v>
       </c>
       <c r="J46" t="n">
-        <v>3.850478649139404</v>
+        <v>4.120008945465088</v>
       </c>
       <c r="K46" t="n">
-        <v>4.682827711105347</v>
+        <v>4.377337455749512</v>
       </c>
       <c r="L46" t="n">
-        <v>4.160032534599305</v>
+        <v>4.31132743358612</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.72719144821167</v>
+        <v>4.685565710067749</v>
       </c>
       <c r="C47" t="n">
-        <v>3.503380537033081</v>
+        <v>4.698522090911865</v>
       </c>
       <c r="D47" t="n">
-        <v>4.831437587738037</v>
+        <v>4.445666551589966</v>
       </c>
       <c r="E47" t="n">
-        <v>3.749759912490845</v>
+        <v>3.664161205291748</v>
       </c>
       <c r="F47" t="n">
-        <v>3.644047260284424</v>
+        <v>4.202317714691162</v>
       </c>
       <c r="G47" t="n">
-        <v>3.508370161056519</v>
+        <v>4.0731201171875</v>
       </c>
       <c r="H47" t="n">
-        <v>4.768104553222656</v>
+        <v>4.025743722915649</v>
       </c>
       <c r="I47" t="n">
-        <v>4.234036922454834</v>
+        <v>4.381320238113403</v>
       </c>
       <c r="J47" t="n">
-        <v>4.040034770965576</v>
+        <v>3.986855268478394</v>
       </c>
       <c r="K47" t="n">
-        <v>3.387181758880615</v>
+        <v>3.64423394203186</v>
       </c>
       <c r="L47" t="n">
-        <v>4.039354491233826</v>
+        <v>4.18075065612793</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.757120609283447</v>
+        <v>4.571842193603516</v>
       </c>
       <c r="C48" t="n">
-        <v>4.842407941818237</v>
+        <v>4.977329015731812</v>
       </c>
       <c r="D48" t="n">
-        <v>4.31826376914978</v>
+        <v>4.399811029434204</v>
       </c>
       <c r="E48" t="n">
-        <v>4.213037967681885</v>
+        <v>4.496085166931152</v>
       </c>
       <c r="F48" t="n">
-        <v>4.305296659469604</v>
+        <v>4.504025936126709</v>
       </c>
       <c r="G48" t="n">
-        <v>4.823953866958618</v>
+        <v>4.884550333023071</v>
       </c>
       <c r="H48" t="n">
-        <v>4.552645206451416</v>
+        <v>4.581342935562134</v>
       </c>
       <c r="I48" t="n">
-        <v>4.656911134719849</v>
+        <v>4.478166341781616</v>
       </c>
       <c r="J48" t="n">
-        <v>4.53621244430542</v>
+        <v>4.387833595275879</v>
       </c>
       <c r="K48" t="n">
-        <v>5.310679912567139</v>
+        <v>4.518011808395386</v>
       </c>
       <c r="L48" t="n">
-        <v>4.63165295124054</v>
+        <v>4.579899835586548</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.275397777557373</v>
+        <v>4.519987344741821</v>
       </c>
       <c r="C49" t="n">
-        <v>3.916312694549561</v>
+        <v>4.500049591064453</v>
       </c>
       <c r="D49" t="n">
-        <v>4.582087278366089</v>
+        <v>4.575905084609985</v>
       </c>
       <c r="E49" t="n">
-        <v>4.421481132507324</v>
+        <v>3.89857292175293</v>
       </c>
       <c r="F49" t="n">
-        <v>4.434482336044312</v>
+        <v>4.458142518997192</v>
       </c>
       <c r="G49" t="n">
-        <v>3.969690084457397</v>
+        <v>4.580329418182373</v>
       </c>
       <c r="H49" t="n">
-        <v>4.401540517807007</v>
+        <v>4.329495906829834</v>
       </c>
       <c r="I49" t="n">
-        <v>4.767079591751099</v>
+        <v>4.429725885391235</v>
       </c>
       <c r="J49" t="n">
-        <v>4.447961807250977</v>
+        <v>4.482074022293091</v>
       </c>
       <c r="K49" t="n">
-        <v>3.863961935043335</v>
+        <v>4.546911239624023</v>
       </c>
       <c r="L49" t="n">
-        <v>4.307999515533448</v>
+        <v>4.432119393348694</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>4.007575273513794</v>
+        <v>3.486621618270874</v>
       </c>
       <c r="C50" t="n">
-        <v>3.862467527389526</v>
+        <v>3.957408905029297</v>
       </c>
       <c r="D50" t="n">
-        <v>3.644523143768311</v>
+        <v>3.899572610855103</v>
       </c>
       <c r="E50" t="n">
-        <v>3.672951698303223</v>
+        <v>3.811285257339478</v>
       </c>
       <c r="F50" t="n">
-        <v>3.504381418228149</v>
+        <v>4.161406755447388</v>
       </c>
       <c r="G50" t="n">
-        <v>3.958193778991699</v>
+        <v>3.925502061843872</v>
       </c>
       <c r="H50" t="n">
-        <v>3.590652942657471</v>
+        <v>4.040711641311646</v>
       </c>
       <c r="I50" t="n">
-        <v>3.619574308395386</v>
+        <v>3.643216848373413</v>
       </c>
       <c r="J50" t="n">
-        <v>4.140458583831787</v>
+        <v>4.185816049575806</v>
       </c>
       <c r="K50" t="n">
-        <v>3.712038516998291</v>
+        <v>3.727548360824585</v>
       </c>
       <c r="L50" t="n">
-        <v>3.771281719207764</v>
+        <v>3.883909010887146</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>3.864668130874634</v>
+        <v>3.925479173660278</v>
       </c>
       <c r="C51" t="n">
-        <v>4.00478720664978</v>
+        <v>4.910008907318115</v>
       </c>
       <c r="D51" t="n">
-        <v>3.970881938934326</v>
+        <v>4.350401639938354</v>
       </c>
       <c r="E51" t="n">
-        <v>3.853212594985962</v>
+        <v>3.987831592559814</v>
       </c>
       <c r="F51" t="n">
-        <v>4.091084957122803</v>
+        <v>4.629220247268677</v>
       </c>
       <c r="G51" t="n">
-        <v>4.622227191925049</v>
+        <v>4.175354480743408</v>
       </c>
       <c r="H51" t="n">
-        <v>4.098075866699219</v>
+        <v>4.662143707275391</v>
       </c>
       <c r="I51" t="n">
-        <v>4.57084584236145</v>
+        <v>3.672161102294922</v>
       </c>
       <c r="J51" t="n">
-        <v>4.972373008728027</v>
+        <v>4.13297700881958</v>
       </c>
       <c r="K51" t="n">
-        <v>4.264631986618042</v>
+        <v>4.488065958023071</v>
       </c>
       <c r="L51" t="n">
-        <v>4.231278872489929</v>
+        <v>4.293364381790161</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.216146783828735</v>
+        <v>4.488588218688965</v>
       </c>
       <c r="C52" t="n">
-        <v>4.193696031570434</v>
+        <v>4.495249266624451</v>
       </c>
       <c r="D52" t="n">
-        <v>4.261276073455811</v>
+        <v>4.408215160369873</v>
       </c>
       <c r="E52" t="n">
-        <v>4.195051455497742</v>
+        <v>4.367974638938904</v>
       </c>
       <c r="F52" t="n">
-        <v>4.260550284385682</v>
+        <v>4.419909443855286</v>
       </c>
       <c r="G52" t="n">
-        <v>4.146647152900695</v>
+        <v>4.452533798217774</v>
       </c>
       <c r="H52" t="n">
-        <v>4.248804149627685</v>
+        <v>4.480457181930542</v>
       </c>
       <c r="I52" t="n">
-        <v>4.302236881256103</v>
+        <v>4.445168585777282</v>
       </c>
       <c r="J52" t="n">
-        <v>4.269100708961487</v>
+        <v>4.412172722816467</v>
       </c>
       <c r="K52" t="n">
-        <v>4.194586691856384</v>
+        <v>4.41163510799408</v>
       </c>
       <c r="L52" t="n">
-        <v>4.228809621334076</v>
+        <v>4.438190412521362</v>
       </c>
     </row>
   </sheetData>
